--- a/single-api/mainapi/swagger_modules.xlsx
+++ b/single-api/mainapi/swagger_modules.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -96,8 +96,13 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -162,6 +167,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0504D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0504D"/>
       </patternFill>
     </fill>
   </fills>
@@ -314,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -440,6 +450,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1325,6 +1338,19 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0% (0/1)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="n"/>
@@ -1517,7 +1543,7 @@
         </is>
       </c>
       <c r="F21" s="29" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
@@ -1526,7 +1552,7 @@
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
-          <t>45% (5/11)</t>
+          <t>82% (9/11)</t>
         </is>
       </c>
     </row>
@@ -1584,6 +1610,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0% (0/25)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="41" t="n"/>
@@ -1606,16 +1645,16 @@
         </is>
       </c>
       <c r="F24" s="29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0/4 PASS；另有1个写操作case未执行</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>44% (4/9)</t>
+          <t>56% (5/9)</t>
         </is>
       </c>
     </row>
@@ -1674,16 +1713,16 @@
         </is>
       </c>
       <c r="F26" s="29" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>15/16 PASS；另有5个写操作case未执行</t>
         </is>
       </c>
       <c r="H26" s="29" t="inlineStr">
         <is>
-          <t>28% (5/18)</t>
+          <t>83% (15/18)</t>
         </is>
       </c>
     </row>
@@ -2320,16 +2359,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>104/111 PASS；另有5个写操作case未执行</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>92% (91/99)</t>
+          <t>96% (95/99)</t>
         </is>
       </c>
     </row>
@@ -2422,16 +2461,16 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>178/185 PASS；另有7个写操作case未执行</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>93% (99/106)</t>
+          <t>100% (106/106)</t>
         </is>
       </c>
     </row>
@@ -2626,16 +2665,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>43/44 PASS；另有6个写操作case未执行</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>64% (18/28)</t>
+          <t>82% (23/28)</t>
         </is>
       </c>
     </row>
@@ -3101,6 +3140,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="41" t="n"/>
@@ -3497,16 +3549,16 @@
         </is>
       </c>
       <c r="F80" s="29" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G80" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="H80" s="29" t="inlineStr">
         <is>
-          <t>61% (14/23)</t>
+          <t>100% (23/23)</t>
         </is>
       </c>
     </row>
@@ -3531,11 +3583,11 @@
         </is>
       </c>
       <c r="F81" s="29" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G81" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>21/21 PASS；另有6个写操作case未执行</t>
         </is>
       </c>
       <c r="H81" s="29" t="inlineStr">
@@ -3633,11 +3685,11 @@
         </is>
       </c>
       <c r="F84" s="29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
@@ -3700,6 +3752,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="41" t="n"/>
@@ -3891,6 +3956,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="41" t="n"/>
@@ -4490,6 +4568,19 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F110" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>未执行</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="41" t="n"/>
@@ -4716,16 +4807,16 @@
         </is>
       </c>
       <c r="F117" s="29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7/9 PASS；另有5个写操作case未执行</t>
         </is>
       </c>
       <c r="H117" s="29" t="inlineStr">
         <is>
-          <t>14% (3/22)</t>
+          <t>41% (9/22)</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5064,6 +5155,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="39.5" customWidth="1" min="5" max="5"/>
     <col width="50.5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="21.95" customHeight="1">
@@ -5095,6 +5187,11 @@
       <c r="F1" s="33" t="inlineStr">
         <is>
           <t>场景覆盖</t>
+        </is>
+      </c>
+      <c r="G1" s="46" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -7308,6 +7405,16 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>服务健康检查</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>case路径记为../Health(绕过INDBASEURL的/api/前缀)，与endpoints表/Health不完全匹配，接口覆盖率曾误显示0%，已核实2026-08-13执行PASS，非漏测</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="41" t="n"/>
@@ -7774,6 +7881,11 @@
       <c r="E88" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -7981,10 +8093,10 @@
       </c>
       <c r="F95" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 56.2%
-场景2: SP广告 — 19.8%
-场景3: 不限广告类型 — 4.6%
-场景4: SB+SP广告+含NTB指标 — 3.4%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 56.2% (PASS)
+场景2: 场景2_SP广告 — 19.8% (PASS)
+场景3: 场景3_不限广告类型 — 4.6% (PASS)
+场景4: 场景4_SB+SP广告+含NTB指标 — 3.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8010,6 +8122,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G96" s="44" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="64" customHeight="1">
       <c r="A97" s="41" t="n"/>
@@ -8035,10 +8152,10 @@
       </c>
       <c r="F97" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 59.2%
-场景2: SP广告 — 19.0%
-场景3: 不限广告类型 — 4.6%
-场景4: SB+SP广告+含NTB指标 — 3.8%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 59.2% (PASS)
+场景2: 场景2_SP广告 — 19.0% (PASS)
+场景3: 场景3_不限广告类型 — 4.6% (PASS)
+场景4: 场景4_SB+SP广告+含NTB指标 — 3.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8066,10 +8183,10 @@
       </c>
       <c r="F98" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+按分组+Prompt状态汇总 — 20.8%
-场景2: SP广告+含NTB指标 — 20.2%
-场景3: 不限广告类型+按分组维度汇总 — 9.4%
-场景4: SP广告+按分组维度汇总 — 9.0%</t>
+          <t>场景1: 场景1_SP广告+按分组+Prompt状态汇总 — 20.8% (PASS)
+场景2: 场景2_SP广告+含NTB指标 — 20.2% (PASS)
+场景3: 场景3_不限广告类型+按分组维度汇总 — 9.4% (PASS)
+场景4: 场景4_SP广告+按分组维度汇总 — 9.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8097,10 +8214,10 @@
       </c>
       <c r="F99" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告 — 40.7%
-场景2: SP广告+含NTB指标 — 37.0%
-场景3: SB广告+含NTB指标 — 7.4%
-场景4: SB+SP广告+含NTB指标 — 3.7%</t>
+          <t>场景1: 场景1_SP广告 — 40.7% (PASS)
+场景2: 场景2_SP广告+含NTB指标 — 37.0% (PASS)
+场景3: 场景3_SB广告+含NTB指标 — 7.4% (PASS)
+场景4: 场景4_SB+SP广告+含NTB指标 — 3.7% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8128,10 +8245,10 @@
       </c>
       <c r="F100" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 47.4%
-场景2: SP广告 — 23.2%
-场景3: 不限广告类型 — 18.9%
-场景4: SB广告+含NTB指标 — 3.2%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 47.4% (PASS)
+场景2: 场景2_SP广告 — 23.2% (PASS)
+场景3: 场景3_不限广告类型 — 18.9% (PASS)
+场景4: 场景4_SB广告+含NTB指标 — 3.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8276,7 @@
       </c>
       <c r="F101" s="44" t="inlineStr">
         <is>
-          <t>场景1: 不限广告类型 — 100.0%</t>
+          <t>场景1: 场景1_不限广告类型 — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8187,10 +8304,10 @@
       </c>
       <c r="F102" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+按分组+Prompt状态汇总 — 24.4%
-场景2: 不限广告类型+按分组维度汇总 — 12.2%
-场景3: SP广告+按分组维度汇总 — 10.4%
-场景4: SP广告+按分组+Prompt状态汇总 — 6.0%</t>
+          <t>场景1: 场景1_SP广告+按分组+Prompt状态汇总 — 24.4% (PASS)
+场景2: 场景2_不限广告类型+按分组维度汇总 — 12.2% (PASS)
+场景3: 场景3_SP广告+按分组维度汇总 — 10.4% (PASS)
+场景4: 场景4_SP广告+按分组+Prompt状态汇总 — 6.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8218,10 +8335,10 @@
       </c>
       <c r="F103" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 53.6%
-场景2: SP广告 — 19.4%
-场景3: 不限广告类型 — 5.0%
-场景4: SB+SP广告+含NTB指标 — 4.0%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 53.6% (PASS)
+场景2: 场景2_SP广告 — 19.4% (PASS)
+场景3: 场景3_不限广告类型 — 5.0% (PASS)
+场景4: 场景4_SB+SP广告+含NTB指标 — 4.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8249,10 +8366,10 @@
       </c>
       <c r="F104" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标+含PromptText过滤 — 51.9%
-场景2: SP广告+含PromptText过滤 — 22.4%
-场景3: 不限广告类型+含PromptText过滤 — 7.1%
-场景4: SP广告+含NTB指标+含PromptText过滤 — 1.9%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标+含PromptText过滤 — 51.9% (PASS)
+场景2: 场景2_SP广告+含PromptText过滤 — 22.4% (PASS)
+场景3: 场景3_不限广告类型+含PromptText过滤 — 7.1% (PASS)
+场景4: 场景4_SP广告+含NTB指标+含PromptText过滤 — 1.9% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8280,10 +8397,10 @@
       </c>
       <c r="F105" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告 — 73.0%
-场景2: 不限广告类型 — 4.4%
-场景3: SB+SP广告 — 4.0%
-场景4: SP广告+指定ASIN过滤 — 3.0%</t>
+          <t>场景1: 场景1_SP广告 — 73.0% (PASS)
+场景2: 场景2_不限广告类型 — 4.4% (PASS)
+场景3: 场景3_SB+SP广告 — 4.0% (PASS)
+场景4: 场景4_SP广告+指定ASIN过滤 — 3.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8311,10 +8428,10 @@
       </c>
       <c r="F106" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 42.5%
-场景2: SP广告 — 30.0%
-场景3: SB广告+含NTB指标 — 7.5%
-场景4: SP广告+含NTB指标+指定Campaign过滤 — 7.5%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 42.5% (PASS)
+场景2: 场景2_SP广告 — 30.0% (PASS)
+场景3: 场景3_SB广告+含NTB指标 — 7.5% (PASS)
+场景4: 场景4_SP广告+含NTB指标+指定Campaign过滤 — 7.5% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8342,10 +8459,10 @@
       </c>
       <c r="F107" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告 — 73.0%
-场景2: SB+SP广告 — 6.0%
-场景3: 不限广告类型 — 6.0%
-场景4: SP广告+指定ASIN过滤 — 3.2%</t>
+          <t>场景1: 场景1_SP广告 — 73.0% (PASS)
+场景2: 场景2_SB+SP广告 — 6.0% (PASS)
+场景3: 场景3_不限广告类型 — 6.0% (PASS)
+场景4: 场景4_SP广告+指定ASIN过滤 — 3.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8373,10 +8490,10 @@
       </c>
       <c r="F108" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告 — 74.2%
-场景2: 不限广告类型 — 5.4%
-场景3: SB+SP广告 — 5.2%
-场景4: SP广告+指定ASIN过滤 — 2.8%</t>
+          <t>场景1: 场景1_SP广告 — 74.2% (PASS)
+场景2: 场景2_不限广告类型 — 5.4% (PASS)
+场景3: 场景3_SB+SP广告 — 5.2% (PASS)
+场景4: 场景4_SP广告+指定ASIN过滤 — 2.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8404,10 +8521,10 @@
       </c>
       <c r="F109" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 56.2%
-场景2: SP广告 — 17.6%
-场景3: 不限广告类型 — 7.6%
-场景4: SB+SP广告+含NTB指标 — 3.4%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 56.2% (PASS)
+场景2: 场景2_SP广告 — 17.6% (PASS)
+场景3: 场景3_不限广告类型 — 7.6% (PASS)
+场景4: 场景4_SB+SP广告+含NTB指标 — 3.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8435,10 +8552,10 @@
       </c>
       <c r="F110" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP广告+含NTB指标 — 16.8%
-场景2: SP广告+含NTB指标 — 13.2%
-场景3: SP广告+按分组+Prompt状态汇总 — 11.6%
-场景4: 不限广告类型+按分组维度汇总 — 8.4%</t>
+          <t>场景1: 场景1_SP广告+含NTB指标 — 16.8% (PASS)
+场景2: 场景2_SP广告+含NTB指标 — 13.2% (PASS)
+场景3: 场景3_SP广告+按分组+Prompt状态汇总 — 11.6% (PASS)
+场景4: 场景4_不限广告类型+按分组维度汇总 — 8.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8731,9 +8848,10 @@
       </c>
       <c r="F120" s="44" t="inlineStr">
         <is>
-          <t>场景1: 按百分比批量调整竞价 Type0 — 48%
-场景2: 固定竞价批量更新 Type1 — 31%
-场景3: 应用建议出价 Type4 — 13%</t>
+          <t>场景1: 场景1_按百分比批量调整竞价_Type0 — 48% (PASS)
+场景2: 场景2_固定竞价批量更新_Type1 — 31% (PASS)
+场景3: 场景3_应用建议出价_Type4 — 13% (PASS)
+场景4: 场景1_【高风险-仅生成不执行】应用系统建议出价(含后置清理,未执行)</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8879,12 @@
       </c>
       <c r="F121" s="44" t="inlineStr">
         <is>
-          <t>场景1: 批量暂停Target — 67%
-场景2: 批量启用Target — 29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
+          <t>场景1: 场景1_批量暂停Target — 67% (PASS)
+场景2: 场景2_批量启用Target — 29% (PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1">
       <c r="A122" s="41" t="n"/>
       <c r="B122" s="22" t="inlineStr">
         <is>
@@ -8788,8 +8906,18 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="123">
+      <c r="F122" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_【高风险-仅生成不执行】应用系统建议出价(含后置清理,未执行)</t>
+        </is>
+      </c>
+      <c r="G122" s="44" t="inlineStr">
+        <is>
+          <t>已生成case(未执行)：写操作，会真实修改测试账号Target出价且新出价由后端算法计算无法预知，无法安全预演回滚，需人工评估后手动执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="96" customHeight="1">
       <c r="A123" s="41" t="n"/>
       <c r="B123" s="23" t="inlineStr">
         <is>
@@ -8809,6 +8937,16 @@
       <c r="E123" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F123" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_无过滤_默认视图_US — 45.2% (PASS)
+场景2: 场景2_指定Campaign过滤_US — 36.8% (PASS)
+场景3: 场景3_带条件过滤(ROAS)_US — 6.0% (PASS)
+场景4: 场景4_指定Campaign+TargetTypes过滤_US — 5.6% (PASS)
+场景5: 场景5_单Campaign详情钻取视图+Filters_US — 3.2% (PASS)
+场景6: 场景6_TargetTypes过滤(不限Campaign)_US — 2.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8836,11 +8974,11 @@
       </c>
       <c r="F124" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单日小时级Target报表 JP市场 — 14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
+          <t>场景1: 场景1_单日小时级Target报表_JP市场 — 14% (PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="112" customHeight="1">
       <c r="A125" s="41" t="n"/>
       <c r="B125" s="23" t="inlineStr">
         <is>
@@ -8862,8 +9000,19 @@
           <t>guguangjie</t>
         </is>
       </c>
-    </row>
-    <row r="126">
+      <c r="F125" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_无过滤_默认汇总_US — 41.6% (PASS)
+场景2: 场景2_指定Campaign过滤汇总_US — 38.2% (PASS)
+场景3: 场景3_TargetTypes过滤汇总(不限Campaign)_US — 5.4% (PASS)
+场景4: 场景4_Filters+Campaign过滤汇总_JP — 4.8% (PASS)
+场景5: 场景5_Campaign+TargetTypes过滤汇总_US — 4.4% (PASS)
+场景6: 场景6_Filters过滤汇总(不限Campaign)_US — 3.4% (PASS)
+场景7: 场景7_Filters+TargetTypes+标签过滤汇总_US — 2.2% (PASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="112" customHeight="1">
       <c r="A126" s="41" t="n"/>
       <c r="B126" s="22" t="inlineStr">
         <is>
@@ -8883,6 +9032,17 @@
       <c r="E126" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F126" s="44" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_指定Campaign过滤趋势图_US — 51.6% (PASS)
+场景2: 场景2_无过滤趋势图_US — 20.6% (PASS)
+场景3: 场景3_Filters过滤趋势图(不限Campaign)_US — 11.2% (PASS)
+场景4: 场景4_TargetTypes过滤趋势图_US — 7.2% (PASS)
+场景5: 场景5_Campaign+TargetTypes过滤+环比对比趋势图_US — 4.0% (PASS)
+场景6: 场景6_Filters+TargetTypes+Portfolio过滤趋势图_US — 2.6% (PASS)
+场景7: 场景7_Filters+Campaign过滤趋势图_US — 2.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -8908,6 +9068,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G127" s="44" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="48" customHeight="1">
       <c r="A128" s="41" t="n"/>
@@ -8933,9 +9098,10 @@
       </c>
       <c r="F128" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单Campaign默认视图 ytd US Spend降序 — 35%
-场景2: 跨账号ROAS+Spend过滤 多Profile — 5%
-场景3: JP市场关键词文本精确过滤 — 14%</t>
+          <t>场景1: 场景1_单Campaign默认视图_ytd_US_Spend降序 — 35% (PASS)
+场景2: 场景2_跨账号ROAS+Spend过滤_多Profile — 5% (PASS)
+场景3: 场景3_JP市场关键词文本精确过滤 — 14% (PASS)
+场景4: 场景1_【高风险-仅生成不执行】应用系统建议出价(含后置清理,未执行)</t>
         </is>
       </c>
     </row>
@@ -8963,8 +9129,8 @@
       </c>
       <c r="F129" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单Campaign汇总行 ytd US — 55%
-场景2: 带ROAS过滤的跨账号汇总 — 20%</t>
+          <t>场景1: 场景1_单Campaign汇总行_ytd_US — 55% (PASS)
+场景2: 场景2_带ROAS过滤的跨账号汇总 — 20% (PASS)</t>
         </is>
       </c>
     </row>
@@ -9257,6 +9423,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="41" t="n"/>
@@ -9280,6 +9451,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="41" t="n"/>
@@ -9303,6 +9479,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="n"/>
@@ -9326,6 +9507,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="41" t="n"/>
@@ -9349,6 +9535,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="41" t="n"/>
@@ -9372,6 +9563,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="n"/>
@@ -9395,6 +9591,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="41" t="n"/>
@@ -9418,6 +9619,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="41" t="n"/>
@@ -9441,6 +9647,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="41" t="n"/>
@@ -9464,6 +9675,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="n"/>
@@ -9487,6 +9703,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="41" t="n"/>
@@ -9510,6 +9731,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="n"/>
@@ -9533,6 +9759,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="41" t="n"/>
@@ -9556,6 +9787,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="n"/>
@@ -9579,6 +9815,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="n"/>
@@ -9602,6 +9843,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="41" t="n"/>
@@ -9625,6 +9871,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="n"/>
@@ -9648,6 +9899,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="n"/>
@@ -9671,6 +9927,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="n"/>
@@ -9694,6 +9955,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="41" t="n"/>
@@ -9717,6 +9983,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="n"/>
@@ -9740,6 +10011,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="41" t="n"/>
@@ -9763,6 +10039,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="41" t="n"/>
@@ -9786,6 +10067,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="n"/>
@@ -9809,6 +10095,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="n"/>
@@ -9832,6 +10123,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="41" t="n"/>
@@ -9857,7 +10153,7 @@
       </c>
       <c r="F28" s="44" t="inlineStr">
         <is>
-          <t>冒烟测试(dev环境样本,非真实客户场景)</t>
+          <t>场景1: 冒烟测试(dev环境样本,非真实客户场景) (FAIL)</t>
         </is>
       </c>
     </row>
@@ -9885,7 +10181,7 @@
       </c>
       <c r="F29" s="44" t="inlineStr">
         <is>
-          <t>冒烟测试(dev环境样本,非真实客户场景)</t>
+          <t>场景1: 冒烟测试(dev环境样本,非真实客户场景) (FAIL)</t>
         </is>
       </c>
     </row>
@@ -9911,6 +10207,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="41" t="n"/>
@@ -9936,7 +10237,7 @@
       </c>
       <c r="F31" s="44" t="inlineStr">
         <is>
-          <t>冒烟测试(dev环境样本,默认分页,非真实客户场景)</t>
+          <t>场景1: 冒烟测试(dev环境样本,默认分页,非真实客户场景) (FAIL)</t>
         </is>
       </c>
     </row>
@@ -9962,6 +10263,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="41" t="n"/>
@@ -9987,7 +10293,7 @@
       </c>
       <c r="F33" s="44" t="inlineStr">
         <is>
-          <t>冒烟测试(dev环境样本,非真实客户场景)</t>
+          <t>场景1: 冒烟测试(dev环境样本,非真实客户场景) (FAIL)</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10319,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>场景1: AI推荐关键词调价(单个) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="41" t="n"/>
@@ -10039,6 +10350,11 @@
       <c r="F35" t="inlineStr">
         <is>
           <t>冒烟测试(dev环境样本,默认分页,非真实客户场景)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -10830,6 +11146,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>场景1: 批量创建商品集锦+品牌视频广告创意新版本 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="41" t="n"/>
@@ -10855,7 +11176,8 @@
       </c>
       <c r="F64" s="44" t="inlineStr">
         <is>
-          <t>场景1: 批量改广告名(可逆,占比100%) — 100%</t>
+          <t>场景1: 场景1_批量改广告名(可逆,占比100%) — 100% (PASS)
+场景2: 在已有SD广告组下新建广告(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -10881,6 +11203,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>场景1: 创建品牌视频广告创意新版本 — 100% (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="41" t="n"/>
@@ -10904,6 +11231,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="41" t="n"/>
@@ -10927,6 +11259,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>场景1: 创建店铺聚焦广告创意新版本 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="41" t="n"/>
@@ -10950,6 +11287,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>场景1: 创建视频广告创意新版本 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="32.1" customHeight="1">
       <c r="A69" s="41" t="n"/>
@@ -10975,8 +11317,8 @@
       </c>
       <c r="F69" s="44" t="inlineStr">
         <is>
-          <t>场景1: 按Profile+Campaign查广告(占比90%) — 90%
-场景2: 指定Adgroup查广告(占比10%) — 10%</t>
+          <t>场景1: 场景1_按Profile+Campaign查广告(占比90%) — 90% (PASS)
+场景2: 场景2_指定Adgroup查广告(占比10%) — 10% (PASS)</t>
         </is>
       </c>
     </row>
@@ -11004,8 +11346,8 @@
       </c>
       <c r="F70" s="44" t="inlineStr">
         <is>
-          <t>场景1: 广告级逐日趋势(dim=date,占比99%) — 99%
-场景2: Profile汇总(dim=ytd,占比1%) — 1%</t>
+          <t>场景1: 场景1_广告级逐日趋势(dim=date,占比99%) — 99% (PASS)
+场景2: 场景2_Profile汇总(dim=ytd,占比1%) — 1% (PASS)</t>
         </is>
       </c>
     </row>
@@ -11031,6 +11373,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_按Profile+Adgroup查广告(占比100%) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="32.1" customHeight="1">
       <c r="A72" s="41" t="n"/>
@@ -11056,8 +11403,8 @@
       </c>
       <c r="F72" s="44" t="inlineStr">
         <is>
-          <t>场景1: SB广告单活动详情(SbAds,占比96%) — 96%
-场景2: Profile聚合列表(aggregate,占比4%) — 4%</t>
+          <t>场景1: 场景1_SB广告单活动详情(SbAds,占比96%) — 96% (PASS)
+场景2: 场景2_Profile聚合列表(aggregate,占比4%) — 4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -11085,8 +11432,8 @@
       </c>
       <c r="F73" s="44" t="inlineStr">
         <is>
-          <t>场景1: SB广告单活动汇总(SbAds,占比75%) — 75%
-场景2: Profile聚合汇总(aggregate,占比25%) — 25%</t>
+          <t>场景1: 场景1_SB广告单活动汇总(SbAds,占比75%) — 75% (PASS)
+场景2: 场景2_Profile聚合汇总(aggregate,占比25%) — 25% (PASS)</t>
         </is>
       </c>
     </row>
@@ -11112,6 +11459,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_按Profile+AdId查广告版本(占比100%) — 100% (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="41" t="n"/>
@@ -11135,6 +11487,12 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_逐日趋势(dim=date,占比97.5%) — 97.5% (PASS)
+场景2: 场景2_按周趋势(dim=week,占比2.5%) — 2.5% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="41" t="n"/>
@@ -11158,6 +11516,12 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_多创意类型列表(adFormat=PC+SDImage,占比96.5%) — 96.5% (PASS)
+场景2: 场景2_仅ProductCollection创意列表(adFormat=PC,占比3%) — 3% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="41" t="n"/>
@@ -11181,6 +11545,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_按Profile+Campaign+Adgroup分页查广告(占比100%) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="41" t="n"/>
@@ -11204,6 +11573,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="41" t="n"/>
@@ -11227,6 +11601,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>场景1: 批量创建广告创意新版本(edit) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="41" t="n"/>
@@ -11280,8 +11659,8 @@
       </c>
       <c r="F81" s="44" t="inlineStr">
         <is>
-          <t>批量创建ENABLED状态PROMPTS广告扩展(含后置清理) — 94.1%
-批量创建PAUSED状态PROMPTS广告扩展 — 5.9%</t>
+          <t>场景1: 批量创建ENABLED状态PROMPTS广告扩展(含后置清理) — 94.1% (PASS)
+场景2: 批量创建PAUSED状态PROMPTS广告扩展 — 5.9% (PASS)</t>
         </is>
       </c>
     </row>
@@ -11307,6 +11686,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>场景1: 批量创建ENABLED状态PROMPTS广告扩展(含后置清理) — 94.1% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="41" t="n"/>
@@ -11336,6 +11720,11 @@
 批量创建PAUSED状态PROMPTS广告扩展 — 5.9%</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="41" t="n"/>
@@ -11357,6 +11746,11 @@
       <c r="E84" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -11710,10 +12104,10 @@
       </c>
       <c r="F96" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单AdGroup ASIN定向新增 — 29.8%
-场景2: 单AdGroup 自定义SKU编号定向新增 — 20.0%
-场景3: 多AdGroup批量 ASIN定向新增 — 35.4%
-场景4: 多AdGroup批量 自定义SKU编号定向新增 — 14.8%</t>
+          <t>场景1: 场景1_单AdGroup_ASIN定向新增 — 29.8% (FAIL)
+场景2: 场景2_单AdGroup_自定义SKU编号定向新增 — 20.0% (FAIL)
+场景3: 场景3_多AdGroup批量_ASIN定向新增 — 35.4% (FAIL)
+场景4: 场景4_多AdGroup批量_自定义SKU编号定向新增 — 14.8% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -11741,9 +12135,9 @@
       </c>
       <c r="F97" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单个SP广告组少量ASIN添加(1-4个)
-场景2: SP广告组中等批量多规格SKU添加(5-49个)
-场景3: SP广告组大批量SKU导入(≥50个,整店同步)</t>
+          <t>场景1: 场景1_单个SP广告组少量ASIN添加(1-4个) — 59.8% (PASS)
+场景2: 场景2_SP广告组中等批量多规格SKU添加(5-49个) — 20.0% (PASS)
+场景3: 场景3_SP广告组大批量SKU导入(≥50个,整店同步) — 20.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -11771,9 +12165,9 @@
       </c>
       <c r="F98" s="44" t="inlineStr">
         <is>
-          <t>单广告组添加单个ASIN商品定向(含后置归档,可重复) — 27%
-单广告组批量粘贴多个ASIN商品定向(含后置归档,可重复) — 33%
-跨多个广告组批量应用同一ASIN商品定向(含后置归档,可重复) — 40%</t>
+          <t>场景1: 单广告组添加单个ASIN商品定向(含后置归档,可重复) — 27% (FAIL)
+场景2: 单广告组批量粘贴多个ASIN商品定向(含后置归档,可重复) — 33% (FAIL)
+场景3: 跨多个广告组批量应用同一ASIN商品定向(含后置归档,可重复) — 40% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -11799,6 +12193,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="41" t="n"/>
@@ -11822,6 +12221,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="48" customHeight="1">
       <c r="A101" s="41" t="n"/>
@@ -11847,9 +12251,9 @@
       </c>
       <c r="F101" s="44" t="inlineStr">
         <is>
-          <t>Campaign级批量创建否定精确匹配关键词(SP)
-Campaign级批量创建否定词组匹配关键词(SB)
-AdGroup级批量创建否定关键词(SP手动/PAT)</t>
+          <t>场景1: Campaign级批量创建否定精确匹配关键词(SP) (PASS)
+场景2: Campaign级批量创建否定词组匹配关键词(SB) (PASS)
+场景3: AdGroup级批量创建否定关键词(SP手动/PAT) (PASS)</t>
         </is>
       </c>
     </row>
@@ -11877,8 +12281,8 @@
       </c>
       <c r="F102" s="44" t="inlineStr">
         <is>
-          <t>SP广告组仅设置ROAS竞价优化目标(ACOS未设置/高频场景)
-SP手动/PAT广告组同时设置ACOS与ROAS双竞价优化目标(中频场景)</t>
+          <t>场景1: SP广告组仅设置ROAS竞价优化目标(ACOS未设置/高频场景) (PASS)
+场景2: SP手动/PAT广告组同时设置ACOS与ROAS双竞价优化目标(中频场景) (PASS)</t>
         </is>
       </c>
     </row>
@@ -11906,9 +12310,9 @@
       </c>
       <c r="F103" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单ASIN替换 旧目标转Paused 新目标默认 — 90.9%
-场景2: 全字段显式替换 旧目标Archived 新目标Enabled keep=false — 7.07%
-场景3: 保留旧目标keep=true 新增替换目标Paused — 2.02%</t>
+          <t>场景1: 场景1_单ASIN替换_旧目标转Paused_新目标默认 — 90.9% (FAIL)
+场景2: 场景2_全字段显式替换_旧目标Archived_新目标Enabled_keep=false — 7.07% (FAIL)
+场景3: 场景3_保留旧目标keep=true_新增替换目标Paused — 2.02% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -11934,6 +12338,20 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>场景1: 场景1_单AdGroup_ASIN定向新增 — 29.8% (FAIL)
+场景2: 场景2_单AdGroup_自定义SKU编号定向新增 — 20.0% (FAIL)
+场景3: 场景3_多AdGroup批量_ASIN定向新增 — 35.4% (FAIL)
+场景4: 场景4_多AdGroup批量_自定义SKU编号定向新增 — 14.8% (FAIL)
+场景5: 场景1_单个SP广告组少量ASIN添加(1-4个) — 59.8% (FAIL)
+场景6: 场景2_SP广告组中等批量多规格SKU添加(5-49个) — 20.0% (FAIL)
+场景7: 场景3_SP广告组大批量SKU导入(≥50个,整店同步) — 20.2% (FAIL)
+场景8: 单广告组添加单个ASIN商品定向(含后置归档,可重复) — 27% (FAIL)
+场景9: 单广告组批量粘贴多个ASIN商品定向(含后置归档,可重复) — 33% (FAIL)
+场景10: 跨多个广告组批量应用同一ASIN商品定向(含后置归档,可重复) — 40% (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="48" customHeight="1">
       <c r="A105" s="41" t="n"/>
@@ -11959,9 +12377,9 @@
       </c>
       <c r="F105" s="44" t="inlineStr">
         <is>
-          <t>SP单个AdGroup批量改价（高频场景）
-SP多个AdGroup跨Campaign批量改价（中频场景）
-跨广告类型批量改价含SD设置bidOptimization（中频场景）</t>
+          <t>场景1: SP单个AdGroup批量改价（高频场景） (FAIL)
+场景2: SP多个AdGroup跨Campaign批量改价（中频场景） (FAIL)
+场景3: 跨广告类型批量改价含SD设置bidOptimization（中频场景） (FAIL)</t>
         </is>
       </c>
     </row>
@@ -11989,14 +12407,25 @@
       </c>
       <c r="F106" s="44" t="inlineStr">
         <is>
-          <t>场景1: SponsoredProducts通用场景 启用AdGroup
-场景2: SponsoredProducts手动PAT场景 暂停AdGroup
-场景3: SponsoredDisplay场景 切换AdGroup状态
-场景4: SponsoredProducts通用场景 归档AdGroup
-CopyAdGroup SP Manual ToDifferentCampaign — 63.8%
-CopyAdGroup SP Manual SameCampaign Duplicate — 17.7%
-CopyAdGroup SP Auto ToDifferentCampaign — 15.6%
-复制SponsoredDisplay广告组（manual targeting，同campaign内复制）</t>
+          <t>场景1: 场景1_SponsoredProducts通用场景_启用AdGroup — 62.0% (PASS)
+场景2: 场景2_SponsoredProducts手动PAT场景_暂停AdGroup — 24.8% (PASS)
+场景3: 场景3_SponsoredDisplay场景_切换AdGroup状态 — 6.4% (PASS)
+场景4: 场景4_SponsoredProducts通用场景_归档AdGroup — 2.6% (PASS)
+场景5: CopyAdGroup_SP_Manual_ToDifferentCampaign — 63.8% (FAIL)
+场景6: CopyAdGroup_SP_Manual_SameCampaign_Duplicate — 17.7% (PASS)
+场景7: CopyAdGroup_SP_Auto_ToDifferentCampaign — 15.6% (PASS)
+场景8: 场景1_SP手动投放AdGroup单ASIN复制 — 82.4% (PASS)
+场景9: 场景2_SP自动投放AdGroup单ASIN复制 — 6.8% (FAIL)
+场景10: 场景3_SP手动投放AdGroup多ASIN复制 — 8.1% (PASS)
+场景11: 场景1_同Campaign内复制并保持enabled — 100% (PASS)
+场景12: 场景2_同Campaign内复制并保持paused — 48.5% (PASS)
+场景13: 复制SponsoredDisplay广告组（manual targeting，同campaign内复制） (PASS)
+场景14: 复制SD广告组(含创意+ASIN定向,含后置清理,可重复) — 100% (PASS)
+场景15: SB广告组+ProductCollection+phrase关键词(含后置归档,可重复) — 70% (PASS)
+场景16: SB广告组+exact关键词+NegativeKeywords(含后置归档,可重复) — 30% (PASS)
+场景17: SB Video广告-简单结构(仅Products+Videos)(含后置归档,可重复) — 60% (PASS)
+场景18: SB Video广告-完整结构(Brand+LandingPage+BrandLogos)(含后置归档,可重复) — 40% (PASS)
+场景19: 在已有Campaign下创建AdGroup(含后置归档,可重复) — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12022,6 +12451,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="41" t="n"/>
@@ -12047,7 +12481,7 @@
       </c>
       <c r="F108" s="44" t="inlineStr">
         <is>
-          <t>批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复)</t>
+          <t>场景1: 批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复) (PASS)</t>
         </is>
       </c>
     </row>
@@ -12075,9 +12509,9 @@
       </c>
       <c r="F109" s="34" t="inlineStr">
         <is>
-          <t>CopyAdGroup SP Manual ToDifferentCampaign — 63.8%
-CopyAdGroup SP Manual SameCampaign Duplicate — 17.7%
-CopyAdGroup SP Auto ToDifferentCampaign — 15.6%</t>
+          <t>场景1: CopyAdGroup_SP_Manual_ToDifferentCampaign — 63.8% (FAIL)
+场景2: CopyAdGroup_SP_Manual_SameCampaign_Duplicate — 17.7% (PASS)
+场景3: CopyAdGroup_SP_Auto_ToDifferentCampaign — 15.6% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12105,9 +12539,9 @@
       </c>
       <c r="F110" s="44" t="inlineStr">
         <is>
-          <t>场景1: SP手动投放AdGroup单ASIN复制 — 82.4%
-场景2: SP自动投放AdGroup单ASIN复制 — 6.8%
-场景3: SP手动投放AdGroup多ASIN复制 — 8.1%</t>
+          <t>场景1: 场景1_SP手动投放AdGroup单ASIN复制 — 82.4% (PASS)
+场景2: 场景2_SP自动投放AdGroup单ASIN复制 — 6.8% (FAIL)
+场景3: 场景3_SP手动投放AdGroup多ASIN复制 — 8.1% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12135,8 +12569,8 @@
       </c>
       <c r="F111" s="44" t="inlineStr">
         <is>
-          <t>场景1: 同Campaign内复制并保持enabled
-场景2: 同Campaign内复制并保持paused</t>
+          <t>场景1: 场景1_同Campaign内复制并保持enabled — 100% (PASS)
+场景2: 场景2_同Campaign内复制并保持paused — 48.5% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12164,7 +12598,7 @@
       </c>
       <c r="F112" s="34" t="inlineStr">
         <is>
-          <t>复制SponsoredDisplay广告组（manual targeting，同campaign内复制）</t>
+          <t>场景1: 复制SponsoredDisplay广告组（manual targeting，同campaign内复制） (PASS)</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12626,7 @@
       </c>
       <c r="F113" s="44" t="inlineStr">
         <is>
-          <t>复制SD广告组(含创意+ASIN定向,含后置清理,可重复)</t>
+          <t>场景1: 复制SD广告组(含创意+ASIN定向,含后置清理,可重复) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12218,6 +12652,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="303.95" customHeight="1">
       <c r="A115" s="41" t="n"/>
@@ -12243,8 +12682,23 @@
       </c>
       <c r="F115" s="44" t="inlineStr">
         <is>
-          <t>通过全局唯一id查询广告组编辑数据 — 60%
-通过profileId+campaignId+adGroupId组合查询广告组编辑数据 — 10%</t>
+          <t>场景1: SP单个AdGroup批量改价（高频场景） (FAIL)
+场景2: SP多个AdGroup跨Campaign批量改价（中频场景） (FAIL)
+场景3: 跨广告类型批量改价含SD设置bidOptimization（中频场景） (FAIL)
+场景4: 场景1_SponsoredProducts通用场景_启用AdGroup — 62.0% (FAIL)
+场景5: 场景2_SponsoredProducts手动PAT场景_暂停AdGroup — 24.8% (FAIL)
+场景6: 场景3_SponsoredDisplay场景_切换AdGroup状态 — 6.4% (FAIL)
+场景7: 场景4_SponsoredProducts通用场景_归档AdGroup — 2.6% (FAIL)
+场景8: 批量设置SD广告组优化方式为clicks(前置读原值+后置还原,可重复) (FAIL)
+场景9: 低价位默认出价调整(&lt;1,含读原值+还原) — 50.8% (FAIL)
+场景10: 中价位默认出价调整(1~3,含读原值+还原) — 40.9% (FAIL)
+场景11: 高价位默认出价调整(&gt;3,含读原值+还原) — 8.3% (FAIL)
+场景12: SD_AdGroup_Update_Basic_Attributes_NoCostControl (FAIL)
+场景13: SD_AdGroup_Update_EnableCostControl (FAIL)
+场景14: SD_AdGroup_Update_DisableCostControl (FAIL)
+场景15: 批量修改AdGroup名称(含读原值+还原,可重复) (FAIL)
+场景16: 普通改名场景-读取原名后改名并还原 (FAIL)
+场景17: 带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原 (FAIL)</t>
         </is>
       </c>
     </row>
@@ -12272,9 +12726,9 @@
       </c>
       <c r="F116" s="44" t="inlineStr">
         <is>
-          <t>不指定CampaignIds查询全部候选AdGroup — 61.4%
-单个CampaignId查询PAT研究AdGroup — 36.8%
-多个CampaignIds批量查询PAT研究AdGroup — 1.8%</t>
+          <t>场景1: 不指定CampaignIds查询全部候选AdGroup — 61.4% (PASS)
+场景2: 单个CampaignId查询PAT研究AdGroup — 36.8% (PASS)
+场景3: 多个CampaignIds批量查询PAT研究AdGroup — 1.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12300,6 +12754,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="80.09999999999999" customHeight="1">
       <c r="A118" s="41" t="n"/>
@@ -12325,11 +12784,11 @@
       </c>
       <c r="F118" s="44" t="inlineStr">
         <is>
-          <t>SB广告活动详情页-单Campaign级Adgroup趋势图（按周Dim）
-Adgroup列表页-账户级总览趋势图（不筛选任何Campaign/AdGroup）
-AdGroup Tag聚合分析-跨Profile的Tag维度Adgroup趋势图
-Adgroup列表页-按Portfolio筛选后的趋势图
-Adgroup列表页-钻取到指定AdGroup的趋势图</t>
+          <t>场景1: SB广告活动详情页-单Campaign级Adgroup趋势图（按周Dim） — 48.0% (PASS)
+场景2: Adgroup列表页-账户级总览趋势图（不筛选任何Campaign/AdGroup） — 15.2% (PASS)
+场景3: AdGroup Tag聚合分析-跨Profile的Tag维度Adgroup趋势图 — 14.6% (PASS)
+场景4: Adgroup列表页-按Portfolio筛选后的趋势图 — 8.8% (PASS)
+场景5: Adgroup列表页-钻取到指定AdGroup的趋势图 — 4.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12357,10 +12816,10 @@
       </c>
       <c r="F119" s="44" t="inlineStr">
         <is>
-          <t>按Campaign查看AdGroup列表(不限定具体AdGroup) — 43.6%
-AdGroup模块主列表(默认活跃状态,不限Campaign) — 25.8%
-AdGroup模块主列表(按AdGroup标签筛选) — 25.6%
-Campaign详情钻取查看单个AdGroup — 4.2%</t>
+          <t>场景1: 按Campaign查看AdGroup列表(不限定具体AdGroup) — 43.6% (PASS)
+场景2: AdGroup模块主列表(默认活跃状态,不限Campaign) — 25.8% (PASS)
+场景3: AdGroup模块主列表(按AdGroup标签筛选) — 25.6% (PASS)
+场景4: Campaign详情钻取查看单个AdGroup — 4.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12388,9 +12847,9 @@
       </c>
       <c r="F120" s="44" t="inlineStr">
         <is>
-          <t>campaignId查询AdgroupTotal 单campaign汇总
-campaignId加adgroupId查询AdgroupTotal 指定adgroup汇总
-广告类型加状态过滤查询AdgroupTotal 账户级汇总</t>
+          <t>场景1: campaignId查询AdgroupTotal_单campaign汇总 (PASS)
+场景2: campaignId加adgroupId查询AdgroupTotal_指定adgroup汇总 (PASS)
+场景3: 广告类型加状态过滤查询AdgroupTotal_账户级汇总 (PASS)</t>
         </is>
       </c>
     </row>
@@ -12418,9 +12877,9 @@
       </c>
       <c r="F121" s="44" t="inlineStr">
         <is>
-          <t>查询SP手动定位(PAT)广告系列的广告组类型
-查询SP通用广告系列的广告组类型
-查询SD广告系列的广告组类型</t>
+          <t>场景1: 查询SP手动定位(PAT)广告系列的广告组类型 — 100% (PASS)
+场景2: 查询SP通用广告系列的广告组类型 (PASS)
+场景3: 查询SD广告系列的广告组类型 (PASS)</t>
         </is>
       </c>
     </row>
@@ -12448,9 +12907,11 @@
       </c>
       <c r="F122" s="44" t="inlineStr">
         <is>
-          <t>单个SP广告系列查询广告组列表 — 92.7%
-单个SD广告系列查询广告组列表 — 92.7%
-批量多campaignId查询广告组列表 — 7.3%</t>
+          <t>场景1: 场景1_同Campaign内复制并保持enabled — 100% (PASS)
+场景2: 场景2_同Campaign内复制并保持paused — 48.5% (PASS)
+场景3: 单个SP广告系列查询广告组列表 — 92.7% (PASS)
+场景4: 单个SD广告系列查询广告组列表 — 92.7% (PASS)
+场景5: 批量多campaignId查询广告组列表 — 7.3% (PASS)</t>
         </is>
       </c>
     </row>
@@ -12478,9 +12939,9 @@
       </c>
       <c r="F123" s="44" t="inlineStr">
         <is>
-          <t>低价位默认出价调整(&lt;1,含读原值+还原) — 50.8%
-中价位默认出价调整(1~3,含读原值+还原) — 40.9%
-高价位默认出价调整(&gt;3,含读原值+还原) — 8.3%</t>
+          <t>场景1: 低价位默认出价调整(&lt;1,含读原值+还原) — 50.8% (FAIL)
+场景2: 中价位默认出价调整(1~3,含读原值+还原) — 40.9% (FAIL)
+场景3: 高价位默认出价调整(&gt;3,含读原值+还原) — 8.3% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -12508,9 +12969,9 @@
       </c>
       <c r="F124" s="44" t="inlineStr">
         <is>
-          <t>SD AdGroup Update Basic Attributes NoCostControl
-SD AdGroup Update EnableCostControl
-SD AdGroup Update DisableCostControl</t>
+          <t>场景1: SD_AdGroup_Update_Basic_Attributes_NoCostControl (FAIL)
+场景2: SD_AdGroup_Update_EnableCostControl (FAIL)
+场景3: SD_AdGroup_Update_DisableCostControl (FAIL)</t>
         </is>
       </c>
     </row>
@@ -12538,8 +12999,8 @@
       </c>
       <c r="F125" s="44" t="inlineStr">
         <is>
-          <t>普通改名场景-读取原名后改名并还原
-带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原</t>
+          <t>场景1: 普通改名场景-读取原名后改名并还原 (PASS)
+场景2: 带sourceName(Creative Hub来源)的改名场景-读取原名后改名并还原 (PASS)</t>
         </is>
       </c>
     </row>
@@ -12567,7 +13028,7 @@
       </c>
       <c r="F126" s="44" t="inlineStr">
         <is>
-          <t>批量修改AdGroup名称(含读原值+还原,可重复)</t>
+          <t>场景1: 批量修改AdGroup名称(含读原值+还原,可重复) (PASS)</t>
         </is>
       </c>
     </row>
@@ -14333,11 +14794,11 @@
       </c>
       <c r="F187" s="34" t="inlineStr">
         <is>
-          <t>创建分析看板分享链接(含后置清理) — 100%
-场景2: 按指定ID查询分享链接状态 — 21.4%
-编辑分享链接完整信息(含创建+清理) — 100%
-编辑分享链接描述(含创建+清理) — 100%
-编辑分享链接过期时间(含创建+清理) — 100%</t>
+          <t>场景1: 创建分析看板分享链接(含后置清理) — 100% (PASS)
+场景2: 场景2_按指定ID查询分享链接状态 — 21.4% (PASS)
+场景3: 编辑分享链接完整信息(含创建+清理) — 100% (PASS)
+场景4: 编辑分享链接描述(含创建+清理) — 100% (PASS)
+场景5: 编辑分享链接过期时间(含创建+清理) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -14363,6 +14824,15 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>场景1: 创建分析看板分享链接(含后置清理) — 100% (PASS)
+场景2: 场景2_按指定ID查询分享链接状态 — 21.4% (PASS)
+场景3: 编辑分享链接完整信息(含创建+清理) — 100% (PASS)
+场景4: 编辑分享链接描述(含创建+清理) — 100% (PASS)
+场景5: 编辑分享链接过期时间(含创建+清理) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="15.95" customHeight="1">
       <c r="A189" s="41" t="n"/>
@@ -14388,7 +14858,7 @@
       </c>
       <c r="F189" s="34" t="inlineStr">
         <is>
-          <t>按Profile查询品牌/非品牌标签树</t>
+          <t>场景1: 按Profile查询品牌/非品牌标签树 (PASS)</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14886,12 @@
       </c>
       <c r="F190" s="34" t="inlineStr">
         <is>
-          <t>场景1: 不筛选ID查询全部分享链接 — 78.6%</t>
+          <t>场景1: 创建分析看板分享链接(含后置清理) — 100% (PASS)
+场景2: 场景1_不筛选ID查询全部分享链接 — 78.6% (PASS)
+场景3: 场景2_按指定ID查询分享链接状态 — 21.4% (PASS)
+场景4: 编辑分享链接完整信息(含创建+清理) — 100% (PASS)
+场景5: 编辑分享链接描述(含创建+清理) — 100% (PASS)
+场景6: 编辑分享链接过期时间(含创建+清理) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14919,7 @@
       </c>
       <c r="F191" s="34" t="inlineStr">
         <is>
-          <t>保存品牌/非品牌标签设置(含读取原值+还原)</t>
+          <t>场景1: 保存品牌/非品牌标签设置(含读取原值+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -14470,6 +14945,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>场景1: 编辑分享链接完整信息(含创建+清理) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="41" t="n"/>
@@ -14493,6 +14973,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>场景1: 编辑分享链接描述(含创建+清理) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="41" t="n"/>
@@ -14518,11 +15003,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>创建分析看板分享链接(含后置清理) — 100%
-场景2: 按指定ID查询分享链接状态 — 21.4%
-编辑分享链接完整信息(含创建+清理) — 100%
-编辑分享链接描述(含创建+清理) — 100%
-编辑分享链接过期时间(含创建+清理) — 100%</t>
+          <t>场景1: 编辑分享链接过期时间(含创建+清理) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -15876,6 +16357,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>场景1: 按profile列表获取组合预测支出与销售额 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="41" t="n"/>
@@ -15899,6 +16385,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>场景1: 基于历史预测数据推算新增花费下的ACOS与销售额 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="41" t="n"/>
@@ -15922,6 +16413,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>场景1: 获取profile当前预算管理模式 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="41" t="n"/>
@@ -15945,6 +16441,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>场景1: 获取指定tag指定月份的预算分析 (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="41" t="n"/>
@@ -15968,6 +16469,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>场景1: 批量为BudgetLine绑定Calendar (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="41" t="n"/>
@@ -15991,6 +16497,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>场景1: 设置profile预算管理级别(SubTagging) (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="41" t="n"/>
@@ -16014,6 +16525,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>场景1: 校验预算级别设置前的冲突情况 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="41" t="n"/>
@@ -16037,6 +16553,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>场景1: 设置预算级别V3(含pacing/控制/预算集) (PASS)
+场景2: 移除profile预算设置(含后置恢复,保证可重复执行) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="41" t="n"/>
@@ -16060,6 +16582,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>场景1: 设置预算通知邮件规则 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="41" t="n"/>
@@ -16083,6 +16610,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>场景1: 检查tag是否已被预算管理 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="41" t="n"/>
@@ -16106,6 +16638,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>场景1: 新建Calendar(含后置删除,可重复执行) (PASS)
+场景2: 提交每日预算设置(含前置创建Calendar+后置清理) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="41" t="n"/>
@@ -16129,6 +16667,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>场景1: 获取每日预算目标数据 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="41" t="n"/>
@@ -16152,6 +16695,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>场景1: 新建Calendar(含后置删除,可重复执行) (PASS)
+场景2: 提交每日预算设置(含前置创建Calendar+后置清理) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="41" t="n"/>
@@ -16175,6 +16724,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="41" t="n"/>
@@ -16198,6 +16752,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>场景1: 下载预算操作日志Excel (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="41" t="n"/>
@@ -16221,6 +16780,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>场景1: 下载预算导入模板Excel (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="41" t="n"/>
@@ -16244,6 +16808,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>场景1: 下载批量预算设置模板Excel (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="41" t="n"/>
@@ -16267,6 +16836,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>场景1: 下载campaign预算建议Excel (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="41" t="n"/>
@@ -16290,6 +16864,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>场景1: 获取profile下预算相关campaign标签 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="41" t="n"/>
@@ -16313,6 +16892,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算仪表盘数据 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="41" t="n"/>
@@ -16336,6 +16920,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算洞察 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="41" t="n"/>
@@ -16359,6 +16948,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算变更日志(分页) (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="41" t="n"/>
@@ -16382,6 +16976,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算变更日志详情(分页) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="41" t="n"/>
@@ -16405,6 +17004,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>场景1: 获取当前用户预算通知邮件设置 (PASS)
+场景2: 查询当前用户预算通知邮件设置 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="41" t="n"/>
@@ -16428,6 +17033,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算操作日志(分页) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="41" t="n"/>
@@ -16451,6 +17061,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算小组件汇总数据 (PASS)
+场景2: 单Profile+品类份额(SOV)过滤查看预算Widget — 50% (PASS)
+场景3: 多Profile+欠花(Underpacing)视图查看预算Widget — 50% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="41" t="n"/>
@@ -16474,6 +17091,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>场景1: 获取Calendar变更日志(分页) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="41" t="n"/>
@@ -16497,6 +17119,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>场景1: 获取Calendar管理列表(分页) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="41" t="n"/>
@@ -16520,6 +17147,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>场景1: 新建Calendar(含后置删除,可重复执行) (PASS)
+场景2: 获取Calendar名称列表 (PASS)
+场景3: 提交每日预算设置(含前置创建Calendar+后置清理) (PASS)
+场景4: 查询当前用户预算日历名称列表 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="41" t="n"/>
@@ -16543,6 +17178,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>场景1: 获取campaign预算批量操作日志 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="41" t="n"/>
@@ -16566,6 +17206,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>场景1: 获取campaign预算建议(分页) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="41" t="n"/>
@@ -16589,6 +17234,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>场景1: 获取每日预算数据 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="41" t="n"/>
@@ -16612,6 +17262,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>场景1: 获取Calendar编辑详情 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="41" t="n"/>
@@ -16637,7 +17292,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>下载批量预算设置模板Excel</t>
+          <t>场景1: 获取当前财年设置 (PASS)</t>
         </is>
       </c>
     </row>
@@ -16663,6 +17318,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>场景1: 获取预测支出与销售 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="41" t="n"/>
@@ -16686,6 +17346,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>场景1: 获取上月花费(tag/subtag级) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="41" t="n"/>
@@ -16709,6 +17374,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>场景1: 获取按月每日预算启用情况 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="41" t="n"/>
@@ -16732,6 +17402,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>场景1: 获取未选中tag之外的其他campaign信息 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="41" t="n"/>
@@ -16755,6 +17430,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算配速趋势(分页) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="41" t="n"/>
@@ -16778,6 +17458,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>场景1: 获取父级标签列表 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="41" t="n"/>
@@ -16801,6 +17486,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>场景1: 获取profile预算与实际花费对比 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="41" t="n"/>
@@ -16824,6 +17514,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算设置行详情 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="41" t="n"/>
@@ -16847,6 +17542,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算设置行列表 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="41" t="n"/>
@@ -16870,6 +17570,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>场景1: 获取子标签默认预算 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="41" t="n"/>
@@ -16893,6 +17598,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>场景1: 获取子标签月度预算 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="41" t="n"/>
@@ -16916,6 +17626,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>场景1: 获取子标签建议分配额度 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="41" t="n"/>
@@ -16939,6 +17654,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>场景1: 获取标签下的子标签列表 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="41" t="n"/>
@@ -16962,6 +17682,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>场景1: 获取标签预算集合 (PASS)
+场景2: 按Profile查询标签预算设置 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="41" t="n"/>
@@ -16985,6 +17711,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>场景1: 获取标签预算与实际花费对比 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="41" t="n"/>
@@ -17008,6 +17739,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>场景1: 获取花费Top5的campaign每日花费 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="41" t="n"/>
@@ -17031,6 +17767,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>场景1: 获取配速不足标签Top列表 (PASS)
+场景2: 按Profile+月度维度查询欠花Top标签趋势图 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="41" t="n"/>
@@ -17054,6 +17796,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>场景1: 获取配速不足标签洞察 (PASS)
+场景2: 按Profile+日期区间查询欠花标签Insight — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="41" t="n"/>
@@ -17077,6 +17825,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>场景1: 获取年度预算设置 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="41" t="n"/>
@@ -17100,6 +17853,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>场景1: 移除profile预算设置(含后置恢复,保证可重复执行) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="41" t="n"/>
@@ -17123,6 +17881,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>场景1: 重置子标签默认目标 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="41" t="n"/>
@@ -17146,6 +17909,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>场景1: 设置预算分配类型 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="41" t="n"/>
@@ -17169,6 +17937,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>场景1: 设置自动重新启用 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="41" t="n"/>
@@ -17192,6 +17965,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>场景1: 设置自动预算控制 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="41" t="n"/>
@@ -17215,6 +17993,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>场景1: 设置自动预算配速 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="41" t="n"/>
@@ -17238,6 +18021,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>场景1: 设置完整自动预算配置 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="41" t="n"/>
@@ -17261,6 +18049,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>场景1: 设置预算结转 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="41" t="n"/>
@@ -17284,6 +18077,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>场景1: 设置子标签默认目标 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="41" t="n"/>
@@ -17307,6 +18105,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>场景1: 设置财年起止月份 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="41" t="n"/>
@@ -17330,6 +18133,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>场景1: 设置财年预算 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="41" t="n"/>
@@ -17353,6 +18161,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>场景1: 设置月度预算 (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="41" t="n"/>
@@ -17376,6 +18189,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>场景1: 设置子标签预算 (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="41" t="n"/>
@@ -17399,6 +18217,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>场景1: 设置子标签月度目标 (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="41" t="n"/>
@@ -17422,6 +18245,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>场景1: 设置目标ACOS (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="41" t="n"/>
@@ -17445,6 +18273,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>场景1: 设置目标ROAS (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="41" t="n"/>
@@ -17468,6 +18301,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>场景1: 提交每日预算设置(含前置创建Calendar+后置清理) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="41" t="n"/>
@@ -17491,6 +18329,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新campaign最大花费 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="41" t="n"/>
@@ -17514,6 +18357,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新campaign最小花费 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="41" t="n"/>
@@ -17537,6 +18385,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>场景1: 更新profile预算模式 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="41" t="n"/>
@@ -17560,6 +18413,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>场景1: 更新campaign每日预算(批量,含checking) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="41" t="n"/>
@@ -17583,6 +18441,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>场景1: 更新单个campaign最大花费 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="41" t="n"/>
@@ -17606,6 +18469,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>场景1: 更新单个campaign最小花费 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="41" t="n"/>
@@ -17629,6 +18497,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>场景1: 更新最小预算百分比 (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="41" t="n"/>
@@ -17652,6 +18525,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>场景1: 上传批量预算设置Excel模板(multipart文件上传) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="41" t="n"/>
@@ -17675,6 +18553,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="41" t="n"/>
@@ -17698,6 +18581,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>场景1: 获取含启用广告组的campaign列表 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="41" t="n"/>
@@ -17721,6 +18609,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算通知设置(中台集成) (PASS)
+场景2: 查询预算通知设置(中台集成,clientId取自JWT) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="41" t="n"/>
@@ -17744,6 +18638,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>场景1: 获取标签AI信息(中台集成) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="41" t="n"/>
@@ -17767,6 +18666,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>场景1: 获取campaign预算报表(中台集成) (PASS)
+场景2: 按CampaignTag筛选Campaign预算报表(中台集成) — 80% (PASS)
+场景3: 按CampaignIds直接查询Campaign预算报表(中台集成) — 20% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="41" t="n"/>
@@ -17790,6 +18696,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>场景1: 获取campaign预算报表V1(含avgSpend,中台集成) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="41" t="n"/>
@@ -17813,6 +18724,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>场景1: 获取campaign预算报表V2(含avgSpend与hasEnableAdgroup,中台集成) (PASS)
+场景2: 按CampaignTag筛选Campaign预算报表V2(中台集成) — 93% (PASS)
+场景3: 不带CampaignTag查询Profile全量Campaign预算报表V2(中台集成) — 7% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="41" t="n"/>
@@ -17836,6 +18754,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>场景1: 获取campaign标签预算报表(中台集成) (PASS)
+场景2: YTD维度查询CampaignTag预算报表(中台集成) — 83% (PASS)
+场景3: 自定义日期区间(date)查询CampaignTag预算报表(中台集成) — 17% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="41" t="n"/>
@@ -17859,6 +18784,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>场景1: 获取profile预算报表(中台集成) (PASS)
+场景2: YTD维度查询Profile预算报表(中台集成) — 63% (PASS)
+场景3: 按月(monthOfYear)维度查询Profile预算报表(中台集成) — 20% (PASS)
+场景4: 自定义日期区间(date)查询Profile预算报表(中台集成) — 17% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="41" t="n"/>
@@ -17882,6 +18815,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>场景1: 获取预算洞察(中台集成) (PASS)
+场景2: 按Profile+Tag+日期区间查询预算Insight(中台集成) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="41" t="n"/>
@@ -17905,6 +18844,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>场景1: 获取无每日预算设置的campaign列表(中台集成) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="41" t="n"/>
@@ -17928,6 +18872,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>场景1: 按clientId/userId获取profile列表(中台集成) (PASS)
+场景2: 按ClientId查询Profile列表(中台Budget引擎集成) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="41" t="n"/>
@@ -17951,6 +18901,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>场景1: 按userId数组获取profile列表(中台集成) (PASS)
+场景2: 查询当前用户可用Profile列表(中台集成,dashboard展示) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="41" t="n"/>
@@ -17974,6 +18930,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>场景1: 获取用户列表(中台集成) (PASS)
+场景2: 查询ClientId下用户列表(中台集成,clientId取自JWT) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="41" t="n"/>
@@ -17997,6 +18959,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>场景1: 按用户id数组批量获取用户信息(中台集成) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="41" t="n"/>
@@ -18020,6 +18987,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>场景1: 更新campaign状态或每日预算(页面操作调用) (PASS)
+场景2: 中台批量更新Campaign每日预算(含建议后置还原) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="41" t="n"/>
@@ -18043,6 +19016,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="41" t="n"/>
@@ -18066,6 +19044,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>场景1: 中台自动化批量更新Campaign预算/状态(含建议后置还原) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="41" t="n"/>
@@ -18089,6 +19072,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>场景1: 为测试账号Campaign生成月度模拟绩效数据 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="41" t="n"/>
@@ -18112,6 +19100,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>场景1: 为测试账号AdGroup/Keyword生成日级模拟绩效数据 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="41" t="n"/>
@@ -18138,6 +19131,11 @@
       <c r="F340" t="inlineStr">
         <is>
           <t>按profile列表获取组合预测支出与销售额</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -21787,6 +22785,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>场景1: 新增/更新用户级SuperWizard设置(捕获/还原) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="41" t="n"/>
@@ -21810,6 +22813,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>场景1: 按campaignIds为一次性Campaign设置预算调度器(含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="41" t="n"/>
@@ -21833,6 +22841,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>场景1: 向导批量创建SP自动投放Campaign(含后置清理,可重复) — 34.2% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="41" t="n"/>
@@ -21856,6 +22869,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>场景1: 向导批量创建SB关键词投放Campaign(含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="41" t="n"/>
@@ -21879,6 +22897,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>场景1: 按选中Campaign批量应用分时调度(单条真实样本简化)</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="41" t="n"/>
@@ -21902,6 +22925,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>场景1: 按campaignIds批量设置目标ACOS/ROAS(零流量,按Swagger结构构造)</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="41" t="n"/>
@@ -21925,6 +22953,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>场景1: 按campaigns数组+公式化目标区间设置(BulkUpdateCampaignTargetSupportFormula)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="41" t="n"/>
@@ -21948,6 +22981,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>场景1: 按campaignIds批量暂停一次性Campaign(含后置清理,可重复) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="41" t="n"/>
@@ -21971,6 +23009,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 4.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="41" t="n"/>
@@ -21994,6 +23037,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>场景1: SimpleMode创建SP自动投放Campaign(含ASIN+AdGroup)</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="41" t="n"/>
@@ -22017,6 +23065,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>场景1: SP手动广告组新增商品定向PAT(含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="41" t="n"/>
@@ -22040,6 +23093,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 14.9% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="41" t="n"/>
@@ -22063,6 +23121,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="41" t="n"/>
@@ -22086,6 +23149,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="41" t="n"/>
@@ -22109,6 +23177,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="41" t="n"/>
@@ -22132,6 +23205,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="41" t="n"/>
@@ -22155,6 +23233,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="41" t="n"/>
@@ -22178,6 +23261,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="41" t="n"/>
@@ -22201,6 +23289,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>场景1: 新增/更新用户级SuperWizard设置(捕获/还原) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="41" t="n"/>
@@ -22224,6 +23317,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>场景1: 提交一次性Campaign的AutoTarget任务(含单例配置捕获/还原) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="41" t="n"/>
@@ -22247,6 +23345,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>场景1: 批量应用分时调度推荐(零流量,按Swagger结构构造)</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="41" t="n"/>
@@ -22270,6 +23373,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>场景1: 批量新增CampaignExtend记录(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="41" t="n"/>
@@ -22293,6 +23401,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>场景1: 批量新增一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled) (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="41" t="n"/>
@@ -22316,6 +23429,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>场景1: 批量操作模型测试接口(零流量,无请求体)</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="41" t="n"/>
@@ -22339,6 +23457,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新CampaignExtend(IsAuto+CalibrationScale)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="41" t="n"/>
@@ -22362,6 +23485,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新CampaignExtend自动目标ROAS(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="41" t="n"/>
@@ -22385,6 +23513,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新CampaignExtend校准系数(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="41" t="n"/>
@@ -22408,6 +23541,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新CampaignExtend的IsAuto开关(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="41" t="n"/>
@@ -22431,6 +23569,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>场景1: 按campaignIds设置ACOS/ROAS/CPC/CPA(BulkUpdateCampaignTargetACOS_TargetROAS_TargetCPC_TargetCPA)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="41" t="n"/>
@@ -22454,6 +23597,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="41" t="n"/>
@@ -22477,6 +23625,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新一次性ASIN自动目标GPM(isCreate=1,Status=0落地)(一次性ASIN,不可物理删除故落地为disabled) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="41" t="n"/>
@@ -22500,6 +23653,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="41" t="n"/>
@@ -22523,6 +23681,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="41" t="n"/>
@@ -22546,6 +23709,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="41" t="n"/>
@@ -22569,6 +23737,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="41" t="n"/>
@@ -22592,6 +23765,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="41" t="n"/>
@@ -22615,6 +23793,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="41" t="n"/>
@@ -22638,6 +23821,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 12.8% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="41" t="n"/>
@@ -22661,6 +23849,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 11.8% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="41" t="n"/>
@@ -22684,6 +23877,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 6.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="41" t="n"/>
@@ -22707,6 +23905,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="41" t="n"/>
@@ -22730,6 +23933,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 37.5% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="41" t="n"/>
@@ -22753,6 +23961,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="41" t="n"/>
@@ -22776,6 +23989,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 1.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="41" t="n"/>
@@ -22799,6 +24017,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 1.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="41" t="n"/>
@@ -22822,6 +24045,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 1.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="41" t="n"/>
@@ -22845,6 +24073,15 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>场景1: 真实调用场景(空body,由鉴权上下文决定) (PASS)
+场景2: Insert写入AutoTargetConfig(实为按ClientId+UserId的Upsert)(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)
+场景3: Update更新AutoTargetConfig的Frequency/DateRange(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)
+场景4: UpdateStatus切换AutoTargetConfig启停状态(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)
+场景5: 提交一次性Campaign的AutoTarget任务(含单例配置捕获/还原) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="41" t="n"/>
@@ -22868,6 +24105,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 11.7% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="41" t="n"/>
@@ -22891,6 +24133,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>场景1: 从Commerce同步数据并更新自动目标(GetCampaignAutoTargetDataFromCommerceAndUpdateAutoTarget)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="41" t="n"/>
@@ -22914,6 +24161,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="41" t="n"/>
@@ -22937,6 +24189,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 9.5% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="41" t="n"/>
@@ -22960,6 +24217,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="41" t="n"/>
@@ -22983,6 +24245,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 6.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="41" t="n"/>
@@ -23006,6 +24273,23 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 83.3% (PASS)
+场景2: 插入CampaignExtend基线记录(一次性Campaign,含后置清理,可重复) (PASS)
+场景3: 开启CampaignExtend自动出价校准(IsAuto)(一次性Campaign,含后置清理,可重复) (PASS)
+场景4: 更新CampaignExtend校准系数(CalibrationScale)(一次性Campaign,含后置清理,可重复) (PASS)
+场景5: 更新CampaignExtend自动目标ROAS(AutoTargetROAS)(一次性Campaign,含后置清理,可重复) (PASS)
+场景6: 批量更新CampaignExtend(IsAuto+CalibrationScale)(一次性Campaign,含后置清理,可重复) (PASS)
+场景7: 批量更新CampaignExtend校准系数(一次性Campaign,含后置清理,可重复) (PASS)
+场景8: 批量更新CampaignExtend的IsAuto开关(一次性Campaign,含后置清理,可重复) (PASS)
+场景9: 批量更新CampaignExtend自动目标ROAS(一次性Campaign,含后置清理,可重复) (PASS)
+场景10: 批量新增CampaignExtend记录(一次性Campaign,含后置清理,可重复) (PASS)
+场景11: 整体更新CampaignExtend记录(ProfileId/CampaignId/IsAuto/CalibrationScale/AutoTargetROAS)(一次性Campaign,含后置清理,可重复) (PASS)
+场景12: 按data数组更新校准系数并开启IsAuto(UpdateCampaignExtendCalibrationScaleAndOpenIsAuto)(一次性Campaign,含后置清理,可重复) (PASS)
+场景13: 从Commerce同步数据并更新自动目标(GetCampaignAutoTargetDataFromCommerceAndUpdateAutoTarget)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="41" t="n"/>
@@ -23029,6 +24313,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 47.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="41" t="n"/>
@@ -23052,6 +24341,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="41" t="n"/>
@@ -23075,6 +24369,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 23.3% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="41" t="n"/>
@@ -23098,6 +24397,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="41" t="n"/>
@@ -23121,6 +24425,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="41" t="n"/>
@@ -23144,6 +24453,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 10.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="41" t="n"/>
@@ -23167,6 +24481,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="41" t="n"/>
@@ -23190,6 +24509,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 1.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="41" t="n"/>
@@ -23213,6 +24537,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 2.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="41" t="n"/>
@@ -23236,6 +24565,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 17.7% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="41" t="n"/>
@@ -23259,6 +24593,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 2.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="41" t="n"/>
@@ -23282,6 +24621,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 11.8% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="41" t="n"/>
@@ -23305,6 +24649,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 5.5% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="41" t="n"/>
@@ -23328,6 +24677,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 1.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="41" t="n"/>
@@ -23351,6 +24705,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="41" t="n"/>
@@ -23376,7 +24735,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>真实高频入参场景 — 4.4%</t>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
         </is>
       </c>
     </row>
@@ -23402,6 +24761,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 11.3% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="41" t="n"/>
@@ -23425,6 +24789,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="41" t="n"/>
@@ -23448,6 +24817,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 3.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="41" t="n"/>
@@ -23471,6 +24845,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="41" t="n"/>
@@ -23494,6 +24873,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="41" t="n"/>
@@ -23517,6 +24901,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 27.7% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="41" t="n"/>
@@ -23540,6 +24929,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="41" t="n"/>
@@ -23563,6 +24957,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 3.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="41" t="n"/>
@@ -23586,6 +24985,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 3.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="41" t="n"/>
@@ -23609,6 +25013,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 86.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="41" t="n"/>
@@ -23632,6 +25041,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 3.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="41" t="n"/>
@@ -23655,6 +25069,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 83.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="41" t="n"/>
@@ -23678,6 +25097,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 85.2% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="41" t="n"/>
@@ -23701,6 +25125,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="41" t="n"/>
@@ -23724,6 +25153,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>场景1: Insert写入AutoTargetConfig(实为按ClientId+UserId的Upsert)(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="41" t="n"/>
@@ -23747,6 +25181,21 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>场景1: 插入CampaignExtend基线记录(一次性Campaign,含后置清理,可重复) (PASS)
+场景2: 开启CampaignExtend自动出价校准(IsAuto)(一次性Campaign,含后置清理,可重复) (PASS)
+场景3: 更新CampaignExtend校准系数(CalibrationScale)(一次性Campaign,含后置清理,可重复) (PASS)
+场景4: 更新CampaignExtend自动目标ROAS(AutoTargetROAS)(一次性Campaign,含后置清理,可重复) (PASS)
+场景5: 批量更新CampaignExtend(IsAuto+CalibrationScale)(一次性Campaign,含后置清理,可重复) (PASS)
+场景6: 批量更新CampaignExtend校准系数(一次性Campaign,含后置清理,可重复) (PASS)
+场景7: 批量更新CampaignExtend的IsAuto开关(一次性Campaign,含后置清理,可重复) (PASS)
+场景8: 批量更新CampaignExtend自动目标ROAS(一次性Campaign,含后置清理,可重复) (PASS)
+场景9: 整体更新CampaignExtend记录(ProfileId/CampaignId/IsAuto/CalibrationScale/AutoTargetROAS)(一次性Campaign,含后置清理,可重复) (PASS)
+场景10: 按data数组更新校准系数并开启IsAuto(UpdateCampaignExtendCalibrationScaleAndOpenIsAuto)(一次性Campaign,含后置清理,可重复) (PASS)
+场景11: 从Commerce同步数据并更新自动目标(GetCampaignAutoTargetDataFromCommerceAndUpdateAutoTarget)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="41" t="n"/>
@@ -23770,6 +25219,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>场景1: 新增一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="41" t="n"/>
@@ -23793,6 +25247,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>场景1: Excel批量创建Campaign(零流量,按Swagger结构构造)</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="41" t="n"/>
@@ -23816,6 +25275,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>场景1: Excel批量更新Campaign(零流量,按Swagger结构构造)</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="41" t="n"/>
@@ -23839,6 +25303,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.2% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="41" t="n"/>
@@ -23862,6 +25331,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.2% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="41" t="n"/>
@@ -23885,6 +25359,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>场景1: 真实高频入参场景 — 0.2% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="41" t="n"/>
@@ -23908,6 +25387,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>场景1: 同步一次性Campaign的Commerce自动目标数据 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="41" t="n"/>
@@ -23931,6 +25415,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>场景1: Insert写入AutoTargetConfig(实为按ClientId+UserId的Upsert)(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)
+场景2: Update更新AutoTargetConfig的Frequency/DateRange(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)
+场景3: UpdateStatus切换AutoTargetConfig启停状态(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)
+场景4: 提交一次性Campaign的AutoTarget任务(含单例配置捕获/还原) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="41" t="n"/>
@@ -23954,6 +25446,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>场景1: UpdateStatus切换AutoTargetConfig启停状态(捕获原值/验证/还原/复核,ClientId+UserId级单例配置) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="41" t="n"/>
@@ -23977,6 +25474,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>场景1: 整体更新CampaignExtend记录(ProfileId/CampaignId/IsAuto/CalibrationScale/AutoTargetROAS)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="41" t="n"/>
@@ -24000,6 +25502,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>场景1: 更新CampaignExtend自动目标ROAS(AutoTargetROAS)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="41" t="n"/>
@@ -24023,6 +25530,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>场景1: 更新CampaignExtend校准系数(CalibrationScale)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="41" t="n"/>
@@ -24046,6 +25558,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>场景1: 按data数组更新校准系数并开启IsAuto(UpdateCampaignExtendCalibrationScaleAndOpenIsAuto)(一次性Campaign,含后置清理,可重复) (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="41" t="n"/>
@@ -24069,6 +25586,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>场景1: 开启CampaignExtend自动出价校准(IsAuto)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="41" t="n"/>
@@ -24092,6 +25614,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>场景1: 设置目标ACOS/ROAS(UpdateCampaignTarget)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="41" t="n"/>
@@ -24115,6 +25642,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>场景1: 批量设置目标ACOS/ROAS(UpdateCampaignTargetAll)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="41" t="n"/>
@@ -24138,6 +25670,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>场景1: 按campaignTagIds批量设置目标(UpdateCampaignTargetWithTagAll)(一次性Campaign,含后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="41" t="n"/>
@@ -24161,6 +25698,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>场景1: 更新一次性ASIN自动目标配置(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="41" t="n"/>
@@ -24184,6 +25726,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>场景1: 更新一次性ASIN自动目标GPM(Status=0落地)(一次性ASIN,不可物理删除故落地为disabled) (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="41" t="n"/>
@@ -24209,7 +25756,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>新增/更新用户级SuperWizard设置(捕获/还原)</t>
+          <t>场景1: 零流量接口最小可用请求(按swagger schema构造) (PASS)</t>
         </is>
       </c>
     </row>
@@ -25119,6 +26666,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>场景1: 创建SP广告组到SD广告组的映射(含定位+后置清理) — 100.0% (PASS)
+场景2: 为已有映射批量设置标签(含创建测试映射+清理) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="607" ht="16" customHeight="1">
       <c r="A607" s="41" t="n"/>
@@ -25144,7 +26697,7 @@
       </c>
       <c r="F607" s="44" t="inlineStr">
         <is>
-          <t>为已有映射批量设置标签(含创建测试映射+清理)</t>
+          <t>场景1: 为已有映射批量设置标签(含创建测试映射+清理) (PASS)</t>
         </is>
       </c>
     </row>
@@ -25170,6 +26723,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>场景1: 创建新标签(含后置清理) — 100.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="609" ht="16" customHeight="1">
       <c r="A609" s="41" t="n"/>
@@ -25195,7 +26753,7 @@
       </c>
       <c r="F609" s="44" t="inlineStr">
         <is>
-          <t>无筛选下载全部映射 — 25.0%</t>
+          <t>场景1: 无筛选下载全部映射 — 25.0% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -25223,12 +26781,12 @@
       </c>
       <c r="F610" s="44" t="inlineStr">
         <is>
-          <t>场景1: 按ExludeFixedPrice过滤广告组 — 44.4%
-场景2: 按IsFilterKeyword过滤广告组 — 23.4%
-场景3: 按Tactics+TargetingType+市场过滤广告组 — 22.4%
-场景4: 按CampaignTagIds+ExludeFixedPrice过滤广告组 — 5.2%
-场景5: 按CampaignTagIds+IsFilterKeyword过滤广告组 — 2.0%
-场景6: 按TargetingType+市场过滤广告组(不含Tactics) — 1.4%</t>
+          <t>场景1: 场景1_按ExludeFixedPrice过滤广告组 — 44.4% (PASS)
+场景2: 场景2_按IsFilterKeyword过滤广告组 — 23.4% (PASS)
+场景3: 场景3_按Tactics+TargetingType+市场过滤广告组 — 22.4% (PASS)
+场景4: 场景4_按CampaignTagIds+ExludeFixedPrice过滤广告组 — 5.2% (PASS)
+场景5: 场景5_按CampaignTagIds+IsFilterKeyword过滤广告组 — 2.0% (PASS)
+场景6: 场景6_按TargetingType+市场过滤广告组(不含Tactics) — 1.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -25256,7 +26814,9 @@
       </c>
       <c r="F611" s="44" t="inlineStr">
         <is>
-          <t>按Source Profile+日期范围+市场筛选查询映射列表 — 98.6%</t>
+          <t>场景1: 按Source Profile+日期范围+市场筛选查询映射列表 — 98.6% (PASS)
+场景2: 创建SP广告组到SD广告组的映射(含定位+后置清理) — 100.0% (PASS)
+场景3: 为已有映射批量设置标签(含创建测试映射+清理) (PASS)</t>
         </is>
       </c>
     </row>
@@ -25284,7 +26844,8 @@
       </c>
       <c r="F612" s="44" t="inlineStr">
         <is>
-          <t>获取当前用户所有CampaignMapping标签 — 100.0%</t>
+          <t>场景1: 获取当前用户所有CampaignMapping标签 — 100.0% (PASS)
+场景2: 为已有映射批量设置标签(含创建测试映射+清理) (PASS)</t>
         </is>
       </c>
     </row>
@@ -25312,7 +26873,8 @@
       </c>
       <c r="F613" s="44" t="inlineStr">
         <is>
-          <t>创建SP广告组到SD广告组的映射(含定位+后置清理) — 100.0%</t>
+          <t>场景1: 创建SP广告组到SD广告组的映射(含定位+后置清理) — 100.0% (PASS)
+场景2: 为已有映射批量设置标签(含创建测试映射+清理) (PASS)</t>
         </is>
       </c>
     </row>
@@ -25340,7 +26902,7 @@
       </c>
       <c r="F614" s="44" t="inlineStr">
         <is>
-          <t>创建新标签(含后置清理) — 100.0%</t>
+          <t>场景1: 创建新标签(含后置清理) — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -27542,6 +29104,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>场景1: 按ENTITY_ID查询品牌StorePage列表 — 99.6% (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" s="41" t="n"/>
@@ -27565,6 +29132,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>场景1: 按profileId查询Store列表 — 100% (PASS)
+场景2: 按profileId查询品牌Store列表 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" s="41" t="n"/>
@@ -27588,6 +29161,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>场景1: 注册品牌Logo/素材资产到Amazon素材库 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="41" t="n"/>
@@ -27611,6 +29189,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>场景1: 手动ProductCollection广告创建(含前置建活动+后置归档,可重复) — 63.4% (PASS)
+场景2: 创建SB Manual Collection广告(含建议后置归档) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="41" t="n"/>
@@ -27634,6 +29218,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>场景1: 创建SB Product Collection广告(含建议后置归档) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="41" t="n"/>
@@ -27657,6 +29246,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" s="41" t="n"/>
@@ -27680,6 +29274,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>场景1: 创建SB Video广告(含建议后置归档) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" s="41" t="n"/>
@@ -27703,6 +29302,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="41" t="n"/>
@@ -27726,6 +29330,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>场景1: 创建SB Store Spotlight广告(含建议后置归档) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="41" t="n"/>
@@ -27749,6 +29358,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" s="41" t="n"/>
@@ -27772,6 +29386,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>场景1: 按关键词搜索类目 (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="41" t="n"/>
@@ -27795,6 +29414,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>场景1: 按商品URL解析ASIN (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="41" t="n"/>
@@ -27818,6 +29442,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>场景1: 空ASIN列表查询 — 35.0% (PASS)
+场景2: 按真实ASIN获取推荐关键词 — 65.0% (PASS)
+场景3: 按ASIN查询推荐关键词 — 55.0% (PASS)
+场景4: 空ASIN列表查询关键词(isVerifyDuplicate=false) — 43.3% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="705" ht="16" customHeight="1">
       <c r="A705" s="41" t="n"/>
@@ -27843,7 +29475,7 @@
       </c>
       <c r="F705" s="44" t="inlineStr">
         <is>
-          <t>按assetId批量查询素材 — 100%</t>
+          <t>场景1: brandEntityId缺省(undefined)查询素材列表 — 79.6% (PASS)</t>
         </is>
       </c>
     </row>
@@ -27869,6 +29501,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>场景1: 按assetId查询单个素材详情 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="41" t="n"/>
@@ -27892,6 +29529,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>场景1: 批量按assetIds查询素材详情 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" s="41" t="n"/>
@@ -27915,6 +29557,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>场景1: 查询profile关联品牌列表 (PASS)
+场景2: 按profileId查询品牌列表 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="41" t="n"/>
@@ -27938,6 +29586,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>场景1: 查询全量商品类目树 — 100% (PASS)
+场景2: 按国家查询全部类目 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="41" t="n"/>
@@ -27961,6 +29615,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>场景1: 按Store页面URL获取页面内ASIN列表 — 100% (PASS)
+场景2: 按Store Page URL查询页面内ASIN — 88.3% (PASS)
+场景3: 按商品详情页(dp)URL查询ASIN — 11.7% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="41" t="n"/>
@@ -27984,6 +29645,16 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>场景1: SP广告类型按SKU查询商品广告 — 82.4% (PASS)
+场景2: SB广告类型按ASIN查询商品广告 — 12.0% (PASS)
+场景3: SD广告类型查询商品广告 — 5.6% (PASS)
+场景4: 第三方(is1P=0)SP广告按SKU查询商品 — 48.3% (PASS)
+场景5: 一方厂商(is1P=1)SP广告按ASIN查询商品 — 35.0% (PASS)
+场景6: 第三方(is1P=0)SB广告按ASIN查询商品 — 13.3% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" s="41" t="n"/>
@@ -28007,6 +29678,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>场景1: 按ASIN获取推荐类目 — 100% (PASS)
+场景2: 按ASIN列表查询推荐类目 — 95.0% (PASS)
+场景3: 空ASIN列表查询推荐类目 — 5.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="41" t="n"/>
@@ -28030,6 +29708,16 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>场景1: productCollection广告格式关键词出价推荐 — 49.0% (PASS)
+场景2: video广告格式关键词出价推荐 — 33.4% (PASS)
+场景3: ProductCollection广告位+按关键词查询建议出价 — 38.3% (PASS)
+场景4: Video广告位+按关键词查询建议出价 — 35.0% (PASS)
+场景5: ProductCollection广告位+不指定关键词查询建议出价 — 10.0% (PASS)
+场景6: 不指定adFormat+按关键词查询建议出价 — 8.3% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="41" t="n"/>
@@ -28053,6 +29741,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>场景1: SB活动可选ASIN分页查询 — 100% (PASS)
+场景2: 分页查询SB Campaign下ASIN列表 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" s="41" t="n"/>
@@ -28076,6 +29770,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>场景1: 查询profile关联Store列表 (PASS)
+场景2: 按profileId查询品牌Store列表 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="41" t="n"/>
@@ -28104,6 +29804,11 @@
           <t>brandEntityId缺省(undefined)查询素材列表 — 79.6%</t>
         </is>
       </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" s="41" t="n"/>
@@ -28127,6 +29832,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>场景1: 按ASIN列表获取推荐商品 — 100% (PASS)
+场景2: 单ASIN查询推荐商品 — 56.7% (PASS)
+场景3: 少量多ASIN(2-10个)查询推荐商品 — 23.3% (PASS)
+场景4: 大批量多ASIN(&gt;10个)查询推荐商品 — 20.0% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="41" t="n"/>
@@ -28148,6 +29861,11 @@
       <c r="E718" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>场景1: 更新SB Ad创意(品牌名/Logo/ASIN组合) (未执行)</t>
         </is>
       </c>
     </row>
@@ -31676,7 +33394,7 @@
       </c>
       <c r="F831" s="44" t="inlineStr">
         <is>
-          <t>导出Campaign报表(单日Dim=date)</t>
+          <t>场景1: 导出Campaign报表(单日Dim=date) — 100% (FAIL)</t>
         </is>
       </c>
       <c r="G831" s="39" t="inlineStr">
@@ -31709,7 +33427,7 @@
       </c>
       <c r="F832" s="44" t="inlineStr">
         <is>
-          <t>下载已完成任务文件(链式取id)</t>
+          <t>场景1: 下载已完成任务文件(链式取id) (PASS)</t>
         </is>
       </c>
     </row>
@@ -31735,6 +33453,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="834" ht="16" customHeight="1">
       <c r="A834" s="41" t="n"/>
@@ -31760,7 +33483,8 @@
       </c>
       <c r="F834" s="44" t="inlineStr">
         <is>
-          <t>下载中心任务列表分页</t>
+          <t>场景1: 下载中心任务列表分页 (PASS)
+场景2: 下载已完成任务文件(链式取id) (PASS)</t>
         </is>
       </c>
       <c r="G834" t="inlineStr">
@@ -31791,6 +33515,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="41" t="n"/>
@@ -31819,6 +33548,11 @@
           <t>下载已完成任务文件(链式取id)</t>
         </is>
       </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="837" ht="16" customHeight="1">
       <c r="A837" s="41" t="n"/>
@@ -32914,6 +34648,11 @@
       <c r="E874" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>场景1: 服务健康检查 (PASS)</t>
         </is>
       </c>
     </row>
@@ -34280,8 +36019,8 @@
       </c>
       <c r="F922" s="44" t="inlineStr">
         <is>
-          <t>单关键词添加(含后置清理,可重复) — 54%
-多关键词批量添加(含后置清理,可重复) — 46%</t>
+          <t>场景1: 单关键词添加(含后置清理,可重复) — 54% (PASS)
+场景2: 多关键词批量添加(含后置清理,可重复) — 46% (PASS)</t>
         </is>
       </c>
     </row>
@@ -34307,6 +36046,12 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>场景1: 单关键词添加(含后置清理,可重复) — 54% (PASS)
+场景2: 多关键词批量添加(含后置清理,可重复) — 46% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="924" ht="64" customHeight="1">
       <c r="A924" s="41" t="n"/>
@@ -34332,10 +36077,12 @@
       </c>
       <c r="F924" s="44" t="inlineStr">
         <is>
-          <t>JP近期月份(2026-01) — 42%
-JP上月(2025-12) — 33%
-JP较早月份(2026-02) — 13%
-JP历史月份(2025-11) — 13%</t>
+          <t>场景1: JP近期月份(2026-01) — 42% (PASS)
+场景2: JP上月(2025-12) — 33% (PASS)
+场景3: JP较早月份(2026-02) — 13% (PASS)
+场景4: JP历史月份(2025-11) — 13% (PASS)
+场景5: 单关键词添加(含后置清理,可重复) — 54% (PASS)
+场景6: 多关键词批量添加(含后置清理,可重复) — 46% (PASS)</t>
         </is>
       </c>
     </row>
@@ -34363,7 +36110,7 @@
       </c>
       <c r="F925" s="44" t="inlineStr">
         <is>
-          <t>查询关键词总数 — 100%</t>
+          <t>场景1: 查询关键词总数 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -34391,7 +36138,7 @@
       </c>
       <c r="F926" t="inlineStr">
         <is>
-          <t>创建关键词(旧版,含后置归档,可重复)</t>
+          <t>场景1: 创建关键词(旧版,含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -34419,7 +36166,7 @@
       </c>
       <c r="F927" t="inlineStr">
         <is>
-          <t>跨Profile批量创建关键词(含后置归档,可重复)</t>
+          <t>场景1: 跨Profile批量创建关键词(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -34447,11 +36194,11 @@
       </c>
       <c r="F928" s="39" t="inlineStr">
         <is>
-          <t>创建关键词(含后置归档,可重复)
-更新单个关键词出价(含前置创建/后置归档,可重复)
-关键词状态流转(含前置创建/后置归档,可重复)
-应用建议出价(含前置创建/后置归档,可重复)
-批量精确调价(含前置创建/后置归档,可重复)</t>
+          <t>场景1: 创建关键词(含后置归档,可重复)
+场景2: 更新单个关键词出价(含前置创建/后置归档,可重复)
+场景3: 关键词状态流转(含前置创建/后置归档,可重复)
+场景4: 应用建议出价(含前置创建/后置归档,可重复)
+场景5: 批量精确调价(含前置创建/后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -34479,7 +36226,7 @@
       </c>
       <c r="F929" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 23.5%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 23.5%</t>
         </is>
       </c>
     </row>
@@ -34507,7 +36254,7 @@
       </c>
       <c r="F930" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 28.1%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 28.1%</t>
         </is>
       </c>
     </row>
@@ -34535,7 +36282,7 @@
       </c>
       <c r="F931" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 6.4%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 6.4%</t>
         </is>
       </c>
     </row>
@@ -34563,7 +36310,7 @@
       </c>
       <c r="F932" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 16.3%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 16.3%</t>
         </is>
       </c>
     </row>
@@ -34591,7 +36338,7 @@
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 28.6%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 28.6%</t>
         </is>
       </c>
     </row>
@@ -34619,7 +36366,7 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 36.2%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 36.2%</t>
         </is>
       </c>
     </row>
@@ -34647,7 +36394,7 @@
       </c>
       <c r="F935" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 40.4%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 40.4%</t>
         </is>
       </c>
     </row>
@@ -34673,6 +36420,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>场景1: 应用建议出价(含前置创建/后置归档,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" s="41" t="n"/>
@@ -34698,7 +36450,7 @@
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标 — 44.6%</t>
+          <t>场景1: 创建/复制关键词或投放目标 — 44.6%</t>
         </is>
       </c>
     </row>
@@ -34726,7 +36478,7 @@
       </c>
       <c r="F938" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标</t>
+          <t>场景1: 创建/复制关键词或投放目标</t>
         </is>
       </c>
     </row>
@@ -34754,7 +36506,7 @@
       </c>
       <c r="F939" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标</t>
+          <t>场景1: 创建/复制关键词或投放目标</t>
         </is>
       </c>
     </row>
@@ -34782,7 +36534,7 @@
       </c>
       <c r="F940" t="inlineStr">
         <is>
-          <t>按筛选条件批量操作</t>
+          <t>场景1: 按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -34810,7 +36562,7 @@
       </c>
       <c r="F941" t="inlineStr">
         <is>
-          <t>按筛选条件批量操作</t>
+          <t>场景1: 按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -34838,7 +36590,7 @@
       </c>
       <c r="F942" t="inlineStr">
         <is>
-          <t>按筛选条件批量操作</t>
+          <t>场景1: 按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -34866,7 +36618,7 @@
       </c>
       <c r="F943" t="inlineStr">
         <is>
-          <t>按筛选条件批量操作</t>
+          <t>场景1: 按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -34894,7 +36646,7 @@
       </c>
       <c r="F944" t="inlineStr">
         <is>
-          <t>按筛选条件批量操作</t>
+          <t>场景1: 按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -34922,7 +36674,7 @@
       </c>
       <c r="F945" t="inlineStr">
         <is>
-          <t>按筛选条件批量操作</t>
+          <t>场景1: 按筛选条件批量操作</t>
         </is>
       </c>
     </row>
@@ -34948,6 +36700,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>场景1: 批量精确调价(含前置创建/后置归档,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="41" t="n"/>
@@ -34973,7 +36730,7 @@
       </c>
       <c r="F947" t="inlineStr">
         <is>
-          <t>下载节日关键词数据</t>
+          <t>场景1: 下载节日关键词数据 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35001,7 +36758,7 @@
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>检查已存在/新增关键词 — 5.5%</t>
+          <t>场景1: 检查已存在/新增关键词 — 5.5% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35029,7 +36786,7 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>按campaignId查AdGroup列表 — 22.6%</t>
+          <t>场景1: 按campaignId查AdGroup列表 — 22.6% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35057,7 +36814,7 @@
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>按单campaign查关键词AdGroup映射 — 91.2%</t>
+          <t>场景1: 按单campaign查关键词AdGroup映射 — 91.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35085,7 +36842,7 @@
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>查关键词出价景观数据 — 100.0%</t>
+          <t>场景1: 查关键词出价景观数据 — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35113,7 +36870,7 @@
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>按tagIds查campaign</t>
+          <t>场景1: 按tagIds查campaign (PASS)</t>
         </is>
       </c>
     </row>
@@ -35141,8 +36898,8 @@
       </c>
       <c r="F953" s="39" t="inlineStr">
         <is>
-          <t>按TargetTypes=Keyword过滤campaign — 41.6%
-不带类型过滤查全部campaign — 34.8%</t>
+          <t>场景1: 按TargetTypes=Keyword过滤campaign — 41.6% (PASS)
+场景2: 不带类型过滤查全部campaign — 34.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35170,7 +36927,7 @@
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>按profileId查campaign战术(旧版)</t>
+          <t>场景1: 按profileId查campaign战术(旧版) (PASS)</t>
         </is>
       </c>
     </row>
@@ -35198,8 +36955,8 @@
       </c>
       <c r="F955" s="39" t="inlineStr">
         <is>
-          <t>不带state过滤查campaign战术列表 — 61.4%
-按states=enabled过滤 — 36.8%</t>
+          <t>场景1: 不带state过滤查campaign战术列表 — 61.4% (PASS)
+场景2: 按states=enabled过滤 — 36.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35227,7 +36984,7 @@
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>按Tactics查campaign(旧版)</t>
+          <t>场景1: 按Tactics查campaign(旧版) (PASS)</t>
         </is>
       </c>
     </row>
@@ -35255,7 +37012,7 @@
       </c>
       <c r="F957" t="inlineStr">
         <is>
-          <t>按Tactics=T00020查campaign — 5.4%</t>
+          <t>场景1: 按Tactics=T00020查campaign — 5.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35283,7 +37040,7 @@
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>Fead版关键词报表</t>
+          <t>场景1: Fead版关键词报表 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35311,7 +37068,7 @@
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>Fead版关键词汇总</t>
+          <t>场景1: Fead版关键词汇总 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35339,7 +37096,7 @@
       </c>
       <c r="F960" t="inlineStr">
         <is>
-          <t>按keywords数组批量查详情 — 91.1%</t>
+          <t>场景1: 按keywords数组批量查详情 — 91.1% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35367,7 +37124,7 @@
       </c>
       <c r="F961" t="inlineStr">
         <is>
-          <t>按关键词文本查所属campaign数 — 38.8%</t>
+          <t>场景1: 按关键词文本查所属campaign数 — 38.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35395,7 +37152,7 @@
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>关键词看板</t>
+          <t>场景1: 关键词看板 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35423,7 +37180,7 @@
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>按campaign查关键词列表 — 97%</t>
+          <t>场景1: 按campaign查关键词列表 — 97% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35451,7 +37208,7 @@
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>按ASIN查关键词分组 — 57.8%</t>
+          <t>场景1: 按ASIN查关键词分组 — 57.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35479,7 +37236,7 @@
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>关键词表现看板</t>
+          <t>场景1: 关键词表现看板 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35507,7 +37264,7 @@
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>关键词占比看板</t>
+          <t>场景1: 关键词占比看板 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35535,7 +37292,7 @@
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>查关键词标签(带isCheckEdit) — 88.0%</t>
+          <t>场景1: 查关键词标签(带isCheckEdit) — 88.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35563,7 +37320,7 @@
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>关键词标签表现 — 4.2%</t>
+          <t>场景1: 关键词标签表现 — 4.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35591,7 +37348,7 @@
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>按关键词文本批量查标签 — 65.4%</t>
+          <t>场景1: 按关键词文本批量查标签 — 65.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35619,7 +37376,7 @@
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>按关键词文本查标签层级 — 65.7%</t>
+          <t>场景1: 按关键词文本查标签层级 — 65.7% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35647,7 +37404,7 @@
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>关键词文本占比</t>
+          <t>场景1: 关键词文本占比 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35675,7 +37432,7 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>长尾词报表</t>
+          <t>场景1: 长尾词报表 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35703,7 +37460,7 @@
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>长尾词按匹配类型分组报表</t>
+          <t>场景1: 长尾词按匹配类型分组报表 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35731,8 +37488,8 @@
       </c>
       <c r="F974" s="39" t="inlineStr">
         <is>
-          <t>默认聚合趋势图(无过滤) — 9.2%
-按keywordIds过滤趋势图 — 2.8%</t>
+          <t>场景1: 默认聚合趋势图(无过滤) — 9.2% (PASS)
+场景2: 按keywordIds过滤趋势图 — 2.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35760,7 +37517,7 @@
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>单关键词详情趋势图 — 7.4%</t>
+          <t>场景1: 单关键词详情趋势图 — 7.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35788,7 +37545,7 @@
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>全选关键词</t>
+          <t>场景1: 全选关键词 (PASS)</t>
         </is>
       </c>
     </row>
@@ -35816,8 +37573,15 @@
       </c>
       <c r="F977" s="39" t="inlineStr">
         <is>
-          <t>默认聚合报表(无关键词过滤) — 20.8%
-按keywordText过滤报表 — 20.8%</t>
+          <t>场景1: 默认聚合报表(无关键词过滤) — 20.8% (PASS)
+场景2: 按keywordText过滤报表 — 20.8% (PASS)
+场景3: 创建关键词(含后置归档,可重复)
+场景4: 创建关键词(旧版,含后置归档,可重复)
+场景5: 跨Profile批量创建关键词(含后置归档,可重复)
+场景6: 更新单个关键词出价(含前置创建/后置归档,可重复)
+场景7: 关键词状态流转(含前置创建/后置归档,可重复)
+场景8: 应用建议出价(含前置创建/后置归档,可重复)
+场景9: 批量精确调价(含前置创建/后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -35845,7 +37609,7 @@
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>按keywordText过滤汇总 — 8.2%</t>
+          <t>场景1: 按keywordText过滤汇总 — 8.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35873,7 +37637,7 @@
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>按关键词文本查最高CPC</t>
+          <t>场景1: 按关键词文本查最高CPC (PASS)</t>
         </is>
       </c>
     </row>
@@ -35901,7 +37665,7 @@
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>创建/复制关键词或投放目标</t>
+          <t>场景1: 创建/复制关键词或投放目标</t>
         </is>
       </c>
     </row>
@@ -35929,7 +37693,7 @@
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>按小时查平均值 — 50.0%</t>
+          <t>场景1: 按小时查平均值 — 50.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35957,7 +37721,7 @@
       </c>
       <c r="F982" t="inlineStr">
         <is>
-          <t>按关键词文本批量打标签(含后置清理,可重复) — 88.2%</t>
+          <t>场景1: 按关键词文本批量打标签(含后置清理,可重复) — 88.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -35985,7 +37749,7 @@
       </c>
       <c r="F983" t="inlineStr">
         <is>
-          <t>按关键词数组批量搜索</t>
+          <t>场景1: 按关键词数组批量搜索 (PASS)</t>
         </is>
       </c>
     </row>
@@ -36011,6 +37775,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>场景1: 更新单个关键词出价(含前置创建/后置归档,可重复)</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" s="41" t="n"/>
@@ -36036,7 +37805,7 @@
       </c>
       <c r="F985" t="inlineStr">
         <is>
-          <t>应用建议出价</t>
+          <t>场景1: 应用建议出价</t>
         </is>
       </c>
     </row>
@@ -36064,7 +37833,7 @@
       </c>
       <c r="F986" t="inlineStr">
         <is>
-          <t>应用建议出价</t>
+          <t>场景1: 应用建议出价</t>
         </is>
       </c>
     </row>
@@ -36092,13 +37861,13 @@
       </c>
       <c r="F987" s="39" t="inlineStr">
         <is>
-          <t>创建关键词(含后置归档,可重复)
-创建关键词(旧版,含后置归档,可重复)
-跨Profile批量创建关键词(含后置归档,可重复)
-更新单个关键词出价(含前置创建/后置归档,可重复)
-关键词状态流转(含前置创建/后置归档,可重复)
-应用建议出价(含前置创建/后置归档,可重复)
-批量精确调价(含前置创建/后置归档,可重复)</t>
+          <t>场景1: 创建关键词(含后置归档,可重复)
+场景2: 创建关键词(旧版,含后置归档,可重复)
+场景3: 跨Profile批量创建关键词(含后置归档,可重复)
+场景4: 更新单个关键词出价(含前置创建/后置归档,可重复)
+场景5: 关键词状态流转(含前置创建/后置归档,可重复)
+场景6: 应用建议出价(含前置创建/后置归档,可重复)
+场景7: 批量精确调价(含前置创建/后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -36126,7 +37895,7 @@
       </c>
       <c r="F988" t="inlineStr">
         <is>
-          <t>应用建议出价</t>
+          <t>场景1: 应用建议出价</t>
         </is>
       </c>
     </row>
@@ -36241,6 +38010,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="993">
       <c r="A993" s="41" t="n"/>
@@ -36264,6 +38038,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="41" t="n"/>
@@ -36287,6 +38066,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="995" ht="16" customHeight="1">
       <c r="A995" s="41" t="n"/>
@@ -36312,7 +38096,7 @@
       </c>
       <c r="F995" s="44" t="inlineStr">
         <is>
-          <t>Okta OAuth回调</t>
+          <t>场景1: Okta OAuth回调 (FAIL)</t>
         </is>
       </c>
     </row>
@@ -36340,13 +38124,13 @@
       </c>
       <c r="F996" s="44" t="inlineStr">
         <is>
-          <t>Colgate+Commerce OAuth回调 — 51%
-Emerson+Amazon OAuth回调 — 21%
-Emerson+Commerce OAuth回调 — 12%
-Colgate+Amazon OAuth回调 — 10%
-Colgate+Walmart OAuth回调 — 3%
-Tinuiti+Amazon OAuth回调 — 2%
-Colgate+DSP OAuth回调 — 1%</t>
+          <t>场景1: Colgate+Commerce OAuth回调 — 51% (FAIL)
+场景2: Emerson+Amazon OAuth回调 — 21% (FAIL)
+场景3: Emerson+Commerce OAuth回调 — 12% (FAIL)
+场景4: Colgate+Amazon OAuth回调 — 10% (FAIL)
+场景5: Colgate+Walmart OAuth回调 — 3% (FAIL)
+场景6: Tinuiti+Amazon OAuth回调 — 2% (FAIL)
+场景7: Colgate+DSP OAuth回调 — 1% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -36374,12 +38158,12 @@
       </c>
       <c r="F997" s="44" t="inlineStr">
         <is>
-          <t>获取Colgate Okta授权URL — 54.5%
-获取Emerson Okta授权URL — 27.5%
-client=t/login/null — 9.5%
-client=t/login/sign — 2.5%
-client=/login/null — 2%
-client=null — 1%</t>
+          <t>场景1: 获取Colgate Okta授权URL — 54.5% (FAIL)
+场景2: 获取Emerson Okta授权URL — 27.5% (FAIL)
+场景3: client=t/login/null — 9.5% (FAIL)
+场景4: client=t/login/sign — 2.5% (FAIL)
+场景5: client=/login/null — 2% (FAIL)
+场景6: client=null — 1% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -36407,15 +38191,15 @@
       </c>
       <c r="F998" s="44" t="inlineStr">
         <is>
-          <t>Amazon平台OAuth回调 — 35.8%
-Walmart平台OAuth回调 — 29.4%
-Target平台OAuth回调 — 9.4%
-Criteo平台OAuth回调 — 8.2%
-SamsClub平台OAuth回调 — 6%
-Instacart平台OAuth回调 — 3.4%
-DoorDash平台OAuth回调 — 3.2%
-DSP平台OAuth回调 — 2.4%
-Kroger平台OAuth回调 — 1.4%</t>
+          <t>场景1: Amazon平台OAuth回调 — 35.8% (FAIL)
+场景2: Walmart平台OAuth回调 — 29.4% (FAIL)
+场景3: Target平台OAuth回调 — 9.4% (FAIL)
+场景4: Criteo平台OAuth回调 — 8.2% (FAIL)
+场景5: SamsClub平台OAuth回调 — 6% (FAIL)
+场景6: Instacart平台OAuth回调 — 3.4% (FAIL)
+场景7: DoorDash平台OAuth回调 — 3.2% (FAIL)
+场景8: DSP平台OAuth回调 — 2.4% (FAIL)
+场景9: Kroger平台OAuth回调 — 1.4% (FAIL)</t>
         </is>
       </c>
     </row>
@@ -36439,6 +38223,11 @@
       <c r="E999" s="7" t="inlineStr">
         <is>
           <t>guguangjie</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>场景1: AWS Marketplace订阅事件回调(路径待确认) (FAIL)</t>
         </is>
       </c>
     </row>
@@ -36730,6 +38519,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>场景1: 获取分享用Token (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1009">
       <c r="A1009" s="41" t="n"/>
@@ -36753,6 +38547,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>场景1: 批量切换计划预算类型（含前置建/后置删,可重复） (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1010">
       <c r="A1010" s="41" t="n"/>
@@ -36776,6 +38575,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>场景1: 批量更新Card字段（含前置建/后置删,可重复） (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1011" ht="16" customHeight="1">
       <c r="A1011" s="41" t="n"/>
@@ -36801,7 +38605,7 @@
       </c>
       <c r="F1011" s="44" t="inlineStr">
         <is>
-          <t>批量更新Card预算与锁定（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 批量更新Card预算与锁定（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -36829,7 +38633,7 @@
       </c>
       <c r="F1012" s="44" t="inlineStr">
         <is>
-          <t>跨计划批量拆分更新Card（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 跨计划批量拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -36855,6 +38659,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>场景1: 更新单个Card编辑字段（含前置建/后置删,可重复） (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1014" ht="16" customHeight="1">
       <c r="A1014" s="41" t="n"/>
@@ -36880,7 +38689,8 @@
       </c>
       <c r="F1014" s="44" t="inlineStr">
         <is>
-          <t>拉取Reach与Performance预测（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 拉取Reach与Performance预测（含前置建/后置删,可重复） — 100% (PASS)
+场景2: 计算预算分配预测（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -36908,7 +38718,7 @@
       </c>
       <c r="F1015" s="44" t="inlineStr">
         <is>
-          <t>按 Profile 查询媒体计划列表</t>
+          <t>场景1: 按 Profile 查询媒体计划列表 (PASS)</t>
         </is>
       </c>
     </row>
@@ -36936,7 +38746,7 @@
       </c>
       <c r="F1016" s="44" t="inlineStr">
         <is>
-          <t>按用户查询媒体计划列表 — 100%</t>
+          <t>场景1: 按用户查询媒体计划列表 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -36962,6 +38772,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>场景1: 单Card推荐Deals（含前置建/后置删,可重复） — 100% (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="1018" ht="16" customHeight="1">
       <c r="A1018" s="41" t="n"/>
@@ -36987,7 +38802,7 @@
       </c>
       <c r="F1018" s="44" t="inlineStr">
         <is>
-          <t>批量推荐Deals（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 批量推荐Deals（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37013,6 +38828,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>场景1: 计算预算分配预测（含前置建/后置删,可重复） — 100% (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="1020" ht="16" customHeight="1">
       <c r="A1020" s="41" t="n"/>
@@ -37038,7 +38858,24 @@
       </c>
       <c r="F1020" s="44" t="inlineStr">
         <is>
-          <t>新建SP零售媒体计划（含后置清理,可重复） — 85%</t>
+          <t>场景1: 新建SP零售媒体计划（含后置清理,可重复） — 85% (PASS)
+场景2: 查询计划详情及全部Cards（含前置建/后置删,可重复） — 100% (PASS)
+场景3: 更新媒体计划字段（含前置建/后置删,可重复） — 100% (PASS)
+场景4: 切换计划预算类型（含前置建/后置删,可重复） — 100% (PASS)
+场景5: 删除媒体计划及全部Cards（含前置建,可重复） — 100% (PASS)
+场景6: 新增Card到计划（含前置建/后置删,可重复） — 100% (PASS)
+场景7: 删除指定Card（含前置建/后置删,可重复） — 100% (PASS)
+场景8: 按定向类型拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)
+场景9: 批量更新Card预算与锁定（含前置建/后置删,可重复） — 100% (PASS)
+场景10: 跨计划批量拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)
+场景11: 批量推荐Deals（含前置建/后置删,可重复） — 100% (PASS)
+场景12: 拉取Reach与Performance预测（含前置建/后置删,可重复） — 100% (PASS)
+场景13: 批量切换计划预算类型（含前置建/后置删,可重复） (PASS)
+场景14: 批量更新Card字段（含前置建/后置删,可重复） (PASS)
+场景15: 更新单个Card编辑字段（含前置建/后置删,可重复） (PASS)
+场景16: 单Card推荐Deals（含前置建/后置删,可重复） — 100% (PASS)
+场景17: 计算预算分配预测（含前置建/后置删,可重复） — 100% (PASS)
+场景18: 复制媒体计划及全部Cards（含前置建/后置删,可重复） (PASS)</t>
         </is>
       </c>
     </row>
@@ -37064,6 +38901,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>场景1: 代理调用Amazon Performance预测（需真实Amazon账号,仅生成不确保通过） (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="1022">
       <c r="A1022" s="41" t="n"/>
@@ -37087,6 +38929,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>场景1: 代理调用Amazon Reach预测（需真实Amazon账号,仅生成不确保通过） (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="1023" ht="48" customHeight="1">
       <c r="A1023" s="41" t="n"/>
@@ -37112,9 +38959,7 @@
       </c>
       <c r="F1023" s="44" t="inlineStr">
         <is>
-          <t>查询计划详情及全部Cards（含前置建/后置删,可重复） — 100%
-更新媒体计划字段（含前置建/后置删,可重复） — 100%
-删除媒体计划及全部Cards（含前置建,可重复） — 100%</t>
+          <t>场景1: 更新媒体计划字段（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37142,9 +38987,14 @@
       </c>
       <c r="F1024" s="44" t="inlineStr">
         <is>
-          <t>查询计划详情及全部Cards（含前置建/后置删,可重复） — 100%
-更新媒体计划字段（含前置建/后置删,可重复） — 100%
-删除媒体计划及全部Cards（含前置建,可重复） — 100%</t>
+          <t>场景1: 查询计划详情及全部Cards（含前置建/后置删,可重复） — 100% (PASS)
+场景2: 删除指定Card（含前置建/后置删,可重复） — 100% (PASS)
+场景3: 按定向类型拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)
+场景4: 批量更新Card预算与锁定（含前置建/后置删,可重复） — 100% (PASS)
+场景5: 跨计划批量拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)
+场景6: 批量更新Card字段（含前置建/后置删,可重复） (PASS)
+场景7: 更新单个Card编辑字段（含前置建/后置删,可重复） (PASS)
+场景8: 单Card推荐Deals（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37172,9 +39022,24 @@
       </c>
       <c r="F1025" s="44" t="inlineStr">
         <is>
-          <t>查询计划详情及全部Cards（含前置建/后置删,可重复） — 100%
-更新媒体计划字段（含前置建/后置删,可重复） — 100%
-删除媒体计划及全部Cards（含前置建,可重复） — 100%</t>
+          <t>场景1: 新建SP零售媒体计划（含后置清理,可重复） — 85% (PASS)
+场景2: 查询计划详情及全部Cards（含前置建/后置删,可重复） — 100% (PASS)
+场景3: 更新媒体计划字段（含前置建/后置删,可重复） — 100% (PASS)
+场景4: 切换计划预算类型（含前置建/后置删,可重复） — 100% (PASS)
+场景5: 删除媒体计划及全部Cards（含前置建,可重复） — 100% (PASS)
+场景6: 新增Card到计划（含前置建/后置删,可重复） — 100% (PASS)
+场景7: 删除指定Card（含前置建/后置删,可重复） — 100% (PASS)
+场景8: 按定向类型拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)
+场景9: 批量更新Card预算与锁定（含前置建/后置删,可重复） — 100% (PASS)
+场景10: 跨计划批量拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)
+场景11: 批量推荐Deals（含前置建/后置删,可重复） — 100% (PASS)
+场景12: 拉取Reach与Performance预测（含前置建/后置删,可重复） — 100% (PASS)
+场景13: 批量切换计划预算类型（含前置建/后置删,可重复） (PASS)
+场景14: 批量更新Card字段（含前置建/后置删,可重复） (PASS)
+场景15: 更新单个Card编辑字段（含前置建/后置删,可重复） (PASS)
+场景16: 单Card推荐Deals（含前置建/后置删,可重复） — 100% (PASS)
+场景17: 计算预算分配预测（含前置建/后置删,可重复） — 100% (PASS)
+场景18: 复制媒体计划及全部Cards（含前置建/后置删,可重复） (PASS)</t>
         </is>
       </c>
     </row>
@@ -37202,7 +39067,7 @@
       </c>
       <c r="F1026" s="44" t="inlineStr">
         <is>
-          <t>切换计划预算类型（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 切换计划预算类型（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37228,6 +39093,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>场景1: 复制媒体计划及全部Cards（含前置建/后置删,可重复） (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1028" ht="32" customHeight="1">
       <c r="A1028" s="41" t="n"/>
@@ -37253,8 +39123,7 @@
       </c>
       <c r="F1028" s="44" t="inlineStr">
         <is>
-          <t>新增Card到计划（含前置建/后置删,可重复） — 100%
-删除指定Card（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 新增Card到计划（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37282,8 +39151,7 @@
       </c>
       <c r="F1029" s="44" t="inlineStr">
         <is>
-          <t>新增Card到计划（含前置建/后置删,可重复） — 100%
-删除指定Card（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 删除指定Card（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37311,7 +39179,7 @@
       </c>
       <c r="F1030" s="44" t="inlineStr">
         <is>
-          <t>按定向类型拆分更新Card（含前置建/后置删,可重复） — 100%</t>
+          <t>场景1: 按定向类型拆分更新Card（含前置建/后置删,可重复） — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37339,7 +39207,7 @@
       </c>
       <c r="F1031" s="44" t="inlineStr">
         <is>
-          <t>查询当前用户全部否定关键词列表 — 100%</t>
+          <t>场景1: 查询当前用户全部否定关键词列表 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37367,7 +39235,7 @@
       </c>
       <c r="F1032" s="44" t="inlineStr">
         <is>
-          <t>查询否定关键词应用状态明细(v1)</t>
+          <t>场景1: 查询否定关键词应用状态明细(v1) (PASS)</t>
         </is>
       </c>
     </row>
@@ -37395,7 +39263,7 @@
       </c>
       <c r="F1033" s="44" t="inlineStr">
         <is>
-          <t>查询否定关键词应用状态明细(v2) — 100%</t>
+          <t>场景1: 查询否定关键词应用状态明细(v2) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37423,7 +39291,7 @@
       </c>
       <c r="F1034" s="44" t="inlineStr">
         <is>
-          <t>批量直接创建AdGroup级否定关键词(含创建Campaign+清理) — 100%</t>
+          <t>场景1: 批量直接创建AdGroup级否定关键词(含创建Campaign+清理) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37451,7 +39319,7 @@
       </c>
       <c r="F1035" s="44" t="inlineStr">
         <is>
-          <t>查询Campaign当前关联的否定关键词列表</t>
+          <t>场景1: 查询Campaign当前关联的否定关键词列表 (PASS)</t>
         </is>
       </c>
     </row>
@@ -37479,7 +39347,7 @@
       </c>
       <c r="F1036" s="44" t="inlineStr">
         <is>
-          <t>批量为多个列表添加同一关键词(含创建+清理) — 84.1%</t>
+          <t>场景1: 批量为多个列表添加同一关键词(含创建+清理) — 84.1% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37507,7 +39375,10 @@
       </c>
       <c r="F1037" s="44" t="inlineStr">
         <is>
-          <t>创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100%</t>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9% (PASS)
+场景3: 批量为多个列表添加同一关键词(含创建+清理) — 84.1% (PASS)
+场景4: 删除否定关键词列表(自建自删) (未执行)</t>
         </is>
       </c>
     </row>
@@ -37533,6 +39404,13 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 按CampaignTag批量应用否定关键词列表(含建议后置解除) (未执行)
+场景3: 按Campaign直接应用否定关键词列表(含建议后置解除) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1039">
       <c r="A1039" s="41" t="n"/>
@@ -37556,6 +39434,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 为列表批量新增否定关键词(含后置删除清理) (未执行)
+场景3: 场景1:DeleteType=delete直接删除(自建自删) — 36.2% (未执行)
+场景4: 场景2:DeleteType=archieveDelete先归档再删(自建自删) — 26.1% (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" s="41" t="n"/>
@@ -37579,6 +39465,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9% (PASS)
+场景3: 批量为多个列表添加同一关键词(含创建+清理) — 84.1% (PASS)
+场景4: 删除否定关键词列表(自建自删) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1041">
       <c r="A1041" s="41" t="n"/>
@@ -37602,6 +39496,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 为列表批量新增否定关键词(含后置删除清理) (未执行)
+场景3: 场景1:DeleteType=delete直接删除(自建自删) — 36.2% (未执行)
+场景4: 场景2:DeleteType=archieveDelete先归档再删(自建自删) — 26.1% (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1042" ht="16" customHeight="1">
       <c r="A1042" s="41" t="n"/>
@@ -37627,7 +39529,7 @@
       </c>
       <c r="F1042" s="44" t="inlineStr">
         <is>
-          <t>按Profile查询AdGroup列表 — 100%</t>
+          <t>场景1: 按Profile查询AdGroup列表 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37655,7 +39557,7 @@
       </c>
       <c r="F1043" s="44" t="inlineStr">
         <is>
-          <t>按Campaign查询AdGroup已有否定关键词 — 69.8%</t>
+          <t>场景1: 按Campaign查询AdGroup已有否定关键词 — 69.8% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37683,7 +39585,7 @@
       </c>
       <c r="F1044" s="44" t="inlineStr">
         <is>
-          <t>按Campaign查询AdGroup定位信息 — 64.4%</t>
+          <t>场景1: 按Campaign查询AdGroup定位信息 — 64.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37711,7 +39613,7 @@
       </c>
       <c r="F1045" s="44" t="inlineStr">
         <is>
-          <t>按关键词查询关联品牌列表 — 60.2%</t>
+          <t>场景1: 按关键词查询关联品牌列表 — 60.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37739,7 +39641,7 @@
       </c>
       <c r="F1046" s="44" t="inlineStr">
         <is>
-          <t>查询Campaign否定关键词自动化探索状态 — 100%</t>
+          <t>场景1: 查询Campaign否定关键词自动化探索状态 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37767,7 +39669,7 @@
       </c>
       <c r="F1047" s="44" t="inlineStr">
         <is>
-          <t>按Profile+Level查询可选Campaign列表 — 85.6%</t>
+          <t>场景1: 按Profile+Level查询可选Campaign列表 — 85.6% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37793,6 +39695,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 按Id查询列表已应用AdGroup详情 — 99.6% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1049" ht="16" customHeight="1">
       <c r="A1049" s="41" t="n"/>
@@ -37818,7 +39726,7 @@
       </c>
       <c r="F1049" s="44" t="inlineStr">
         <is>
-          <t>按Id查询列表详情(分享链接场景) — 100%</t>
+          <t>场景1: 按Id查询列表详情(分享链接场景) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37844,6 +39752,15 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9% (PASS)
+场景3: 批量为多个列表添加同一关键词(含创建+清理) — 84.1% (PASS)
+场景4: 按Profile查询否定关键词列表 — 100% (PASS)
+场景5: 删除否定关键词列表(自建自删) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1051" ht="16" customHeight="1">
       <c r="A1051" s="41" t="n"/>
@@ -37869,7 +39786,7 @@
       </c>
       <c r="F1051" s="44" t="inlineStr">
         <is>
-          <t>按CampaignTag查询自动化否定统计 — 100%</t>
+          <t>场景1: 按CampaignTag查询自动化否定统计 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37897,7 +39814,7 @@
       </c>
       <c r="F1052" s="44" t="inlineStr">
         <is>
-          <t>分页查询关键词级应用状态 — 100%</t>
+          <t>场景1: 分页查询关键词级应用状态 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37923,6 +39840,15 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 按Id查询关键词表格(含AppliedCampaigns统计) — 98.8% (PASS)
+场景3: 为列表批量新增否定关键词(含后置删除清理) (未执行)
+场景4: 场景1:DeleteType=delete直接删除(自建自删) — 36.2% (未执行)
+场景5: 场景2:DeleteType=archieveDelete先归档再删(自建自删) — 26.1% (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" s="41" t="n"/>
@@ -37946,6 +39872,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)
+场景2: 按Id查询关键词纯文本列表 — 99.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1055" ht="16" customHeight="1">
       <c r="A1055" s="41" t="n"/>
@@ -37971,7 +39903,7 @@
       </c>
       <c r="F1055" s="44" t="inlineStr">
         <is>
-          <t>为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9%</t>
+          <t>场景1: 为单个Campaign直接应用否定关键词列表(含创建+清理) — 90.9% (PASS)</t>
         </is>
       </c>
     </row>
@@ -37999,7 +39931,7 @@
       </c>
       <c r="F1056" t="inlineStr">
         <is>
-          <t>查询否定关键词应用状态明细(v1)</t>
+          <t>场景1: 创建否定关键词列表完整生命周期(创建+加词+应用+查看+改名+删词+删除) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -38606,7 +40538,7 @@
       </c>
       <c r="F1077" s="44" t="inlineStr">
         <is>
-          <t>邮件通知规则生命周期(创建+查+改+暂停+删除)</t>
+          <t>场景1: 邮件通知规则生命周期(创建+查+改+暂停+删除) (PASS)</t>
         </is>
       </c>
     </row>
@@ -38634,7 +40566,7 @@
       </c>
       <c r="F1078" s="44" t="inlineStr">
         <is>
-          <t>保存预算通知设置(含读取+还原) — 50%</t>
+          <t>场景1: 保存预算通知设置(含读取+还原) — 50% (PASS)</t>
         </is>
       </c>
     </row>
@@ -38660,6 +40592,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>场景1: 邮件通知规则生命周期(创建+查+改+暂停+删除) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" s="41" t="n"/>
@@ -38683,6 +40620,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>场景1: 通用邮件/站内信通知设置生命周期(创建+查+改状态+删除) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1081">
       <c r="A1081" s="41" t="n"/>
@@ -38706,6 +40648,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>场景1: 邮件通知规则生命周期(创建+查+改+暂停+删除) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1082" ht="15.95" customHeight="1">
       <c r="A1082" s="41" t="n"/>
@@ -38731,7 +40678,7 @@
       </c>
       <c r="F1082" s="36" t="inlineStr">
         <is>
-          <t>保存预算通知设置(含读取+还原) — 50%</t>
+          <t>场景1: 保存预算通知设置(含读取+还原) — 50% (PASS)</t>
         </is>
       </c>
     </row>
@@ -38759,7 +40706,7 @@
       </c>
       <c r="F1083" s="36" t="inlineStr">
         <is>
-          <t>保存类型级邮件/站内信告警设置(含读取+还原)</t>
+          <t>场景1: 保存类型级邮件/站内信告警设置(含读取+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -38785,6 +40732,14 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>场景1: 通用邮件/站内信通知设置生命周期(创建+查+改状态+删除) — 100% (PASS)
+场景2: 场景1_查询通用邮件/站内信设置(type=10) — 54.7% (PASS)
+场景3: 场景2_查询通用邮件/站内信设置(type=11) — 32.1% (PASS)
+场景4: 场景3_查询通用邮件/站内信设置(type=14) — 13.2% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1085">
       <c r="A1085" s="41" t="n"/>
@@ -38808,6 +40763,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>场景1: 邮件通知规则生命周期(创建+查+改+暂停+删除) (PASS)
+场景2: 场景1_分页查询邮件通知规则列表 — 100% (FAIL)</t>
+        </is>
+      </c>
     </row>
     <row r="1086" ht="15.95" customHeight="1">
       <c r="A1086" s="41" t="n"/>
@@ -38833,7 +40794,7 @@
       </c>
       <c r="F1086" s="36" t="inlineStr">
         <is>
-          <t>保存超预算邮件提醒设置(含读取+还原) — 100%</t>
+          <t>场景1: 保存超预算邮件提醒设置(含读取+还原) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -38861,7 +40822,7 @@
       </c>
       <c r="F1087" s="36" t="inlineStr">
         <is>
-          <t>保存商品资质邮件提醒设置(含读取+还原)</t>
+          <t>场景1: 保存商品资质邮件提醒设置(含读取+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -38889,7 +40850,7 @@
       </c>
       <c r="F1088" s="44" t="inlineStr">
         <is>
-          <t>查询当前用户可用Profile列表</t>
+          <t>场景1: 查询当前用户可用Profile列表 (PASS)</t>
         </is>
       </c>
     </row>
@@ -38917,7 +40878,7 @@
       </c>
       <c r="F1089" s="44" t="inlineStr">
         <is>
-          <t>保存标签匹配规则提醒设置(含读取+还原)</t>
+          <t>场景1: 保存标签匹配规则提醒设置(含读取+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -38945,7 +40906,7 @@
       </c>
       <c r="F1090" t="inlineStr">
         <is>
-          <t>保存预算通知设置(含读取+还原) — 50%</t>
+          <t>场景1: 保存标签匹配规则提醒设置(含读取+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -38973,7 +40934,7 @@
       </c>
       <c r="F1091" s="44" t="inlineStr">
         <is>
-          <t>保存超预算邮件提醒设置(含读取+还原) — 100%</t>
+          <t>场景1: 保存超预算邮件提醒设置(含读取+还原) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -39001,7 +40962,7 @@
       </c>
       <c r="F1092" s="44" t="inlineStr">
         <is>
-          <t>保存商品资质邮件提醒设置(含读取+还原)</t>
+          <t>场景1: 保存商品资质邮件提醒设置(含读取+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -39029,7 +40990,7 @@
       </c>
       <c r="F1093" s="44" t="inlineStr">
         <is>
-          <t>保存类型级邮件/站内信告警设置(含读取+还原)</t>
+          <t>场景1: 保存类型级邮件/站内信告警设置(含读取+还原) (PASS)</t>
         </is>
       </c>
     </row>
@@ -39057,7 +41018,7 @@
       </c>
       <c r="F1094" s="44" t="inlineStr">
         <is>
-          <t>通用邮件/站内信通知设置生命周期(创建+查+改状态+删除) — 100%</t>
+          <t>场景1: 通用邮件/站内信通知设置生命周期(创建+查+改状态+删除) — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -39083,6 +41044,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>场景1: 通用邮件/站内信通知设置生命周期(创建+查+改状态+删除) — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" s="41" t="n"/>
@@ -39108,7 +41074,7 @@
       </c>
       <c r="F1096" t="inlineStr">
         <is>
-          <t>邮件通知规则生命周期(创建+查+改+暂停+删除)</t>
+          <t>场景1: 邮件通知规则生命周期(创建+查+改+暂停+删除) (PASS)</t>
         </is>
       </c>
     </row>
@@ -39341,6 +41307,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>场景1: 查询Copy Campaign操作日志 — 100% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1105" ht="16" customHeight="1">
       <c r="A1105" s="41" t="n"/>
@@ -39827,6 +41798,11 @@
       <c r="E1121" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>场景1: 销售诊断首页数据 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -42340,6 +44316,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" s="41" t="n"/>
@@ -42363,6 +44344,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1211">
       <c r="A1211" s="41" t="n"/>
@@ -42386,6 +44372,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1212" ht="16" customHeight="1">
       <c r="A1212" s="41" t="n"/>
@@ -42411,7 +44402,7 @@
       </c>
       <c r="F1212" s="44" t="inlineStr">
         <is>
-          <t>按 shareId 查询分享的 Amazon Portfolio — 100%</t>
+          <t>场景1: 按 shareId 查询分享的 Amazon Portfolio — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -42439,7 +44430,7 @@
       </c>
       <c r="F1213" s="44" t="inlineStr">
         <is>
-          <t>按 shareId 查询分享的 Campaign 标签 — 100%</t>
+          <t>场景1: 按 shareId 查询分享的 Campaign 标签 — 100% (PASS)</t>
         </is>
       </c>
     </row>
@@ -42465,6 +44456,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" s="41" t="n"/>
@@ -42488,6 +44484,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" s="41" t="n"/>
@@ -42511,6 +44512,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" s="41" t="n"/>
@@ -42534,6 +44540,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" s="41" t="n"/>
@@ -42557,6 +44568,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" s="41" t="n"/>
@@ -42580,6 +44596,11 @@
           <t>zhanghaobo</t>
         </is>
       </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" s="41" t="n"/>
@@ -42608,6 +44629,11 @@
           <t>按 shareId 查询分享的 Amazon Portfolio — 100%</t>
         </is>
       </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" s="41" t="n"/>
@@ -42629,6 +44655,11 @@
       <c r="E1221" s="4" t="inlineStr">
         <is>
           <t>zhanghaobo</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
         </is>
       </c>
     </row>
@@ -43766,7 +45797,8 @@
       </c>
       <c r="F1261" s="44" t="inlineStr">
         <is>
-          <t>在现有广告组下新建广告(结构占位,待补真实值)</t>
+          <t>场景1: 在现有广告组下新建广告(结构占位,待补真实值) (FAIL)
+场景2: 在已有SD广告组下新建广告(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -43794,7 +45826,8 @@
       </c>
       <c r="F1262" s="44" t="inlineStr">
         <is>
-          <t>在现有活动下新建暂停状态的广告组(点击优化+图片创意) — 20.0%</t>
+          <t>场景1: 在现有活动下新建暂停状态的广告组(点击优化+图片创意) — 20.0% (PASS)
+场景2: 在已有SD Campaign下新建广告组+广告(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -43822,7 +45855,8 @@
       </c>
       <c r="F1263" s="44" t="inlineStr">
         <is>
-          <t>同账号内复制活动(不复制创意)并保持暂停状态 — 18.8%</t>
+          <t>场景1: 同账号内复制活动(不复制创意)并保持暂停状态 — 18.8% (PASS)
+场景2: 同Profile内复制SD广告系列(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -43850,7 +45884,8 @@
       </c>
       <c r="F1264" s="44" t="inlineStr">
         <is>
-          <t>同账号内复制活动及广告组ASIN(含创意)并保持暂停状态 — 41.7%</t>
+          <t>场景1: 同账号内复制活动及广告组ASIN(含创意)并保持暂停状态 — 41.7% (PASS)
+场景2: 同Profile内复制SD广告系列并指定AdGroup+ASIN(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -43878,7 +45913,8 @@
       </c>
       <c r="F1265" s="44" t="inlineStr">
         <is>
-          <t>CPC计费+图片创意+新建广告组的完整活动创建(暂停状态) — 27.6%</t>
+          <t>场景1: CPC计费+图片创意+新建广告组的完整活动创建(暂停状态) — 27.6% (PASS)
+场景2: 创建SD广告系列+广告组+广告(含后置归档,可重复)</t>
         </is>
       </c>
     </row>
@@ -46381,6 +48417,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>场景1: 新增ASIN商品定向Target (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1355">
       <c r="A1355" s="41" t="n"/>
@@ -46404,6 +48445,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>场景1: 批量将目标复制为否定投放 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1356">
       <c r="A1356" s="41" t="n"/>
@@ -46427,6 +48473,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>场景1: 批量应用PAT建议出价 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1357">
       <c r="A1357" s="41" t="n"/>
@@ -46450,6 +48501,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1358">
       <c r="A1358" s="41" t="n"/>
@@ -46473,6 +48529,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>场景1: 批量复制Target到其他广告组 (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1359">
       <c r="A1359" s="41" t="n"/>
@@ -46496,6 +48557,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1360">
       <c r="A1360" s="41" t="n"/>
@@ -46519,6 +48585,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1361" ht="16" customHeight="1">
       <c r="A1361" s="41" t="n"/>
@@ -46544,7 +48615,7 @@
       </c>
       <c r="F1361" s="44" t="inlineStr">
         <is>
-          <t>场景1: SD广告组新增ASIN商品定向PAT(含后置清理,可重复) — 100.0%</t>
+          <t>场景1: 场景1_SD广告组新增ASIN商品定向PAT(含后置清理,可重复) — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -46570,6 +48641,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1363">
       <c r="A1363" s="41" t="n"/>
@@ -46593,6 +48669,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1364">
       <c r="A1364" s="41" t="n"/>
@@ -46616,6 +48697,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1365">
       <c r="A1365" s="41" t="n"/>
@@ -46639,6 +48725,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" s="41" t="n"/>
@@ -46662,6 +48753,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1367">
       <c r="A1367" s="41" t="n"/>
@@ -46685,6 +48781,15 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>场景1: 列表页汇总趋势图(不筛选具体Target,全类型) — 37.8% (FAIL)
+场景2: 按勾选Target筛选的汇总趋势图 — 29.6% (FAIL)
+场景3: 单个PAT Target(SP)按天趋势图 — 24.6% (PASS)
+场景4: 单个PAT Target(小写kindType=pat)按天趋势图 — 5.6% (PASS)
+场景5: 单个SD Audience Target按天趋势图 — 2.4% (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1368">
       <c r="A1368" s="41" t="n"/>
@@ -46708,6 +48813,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1369">
       <c r="A1369" s="41" t="n"/>
@@ -46731,6 +48841,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1370">
       <c r="A1370" s="41" t="n"/>
@@ -46754,6 +48869,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1371">
       <c r="A1371" s="41" t="n"/>
@@ -46777,6 +48897,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>场景1: Excel批量更新Target(状态/出价/表达式) (未执行)</t>
+        </is>
+      </c>
     </row>
     <row r="1372">
       <c r="A1372" s="41" t="n"/>
@@ -46800,6 +48925,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1373">
       <c r="A1373" s="41" t="n"/>
@@ -46823,6 +48953,11 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>零流量(365d 0次)，暂不覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="1374" ht="16" customHeight="1">
       <c r="A1374" s="41" t="n"/>
@@ -46848,7 +48983,7 @@
       </c>
       <c r="F1374" s="44" t="inlineStr">
         <is>
-          <t>场景1: 单PAT目标调整出价</t>
+          <t>场景1: 场景1_单PAT目标调整出价 (PASS)</t>
         </is>
       </c>
     </row>
@@ -46876,8 +49011,10 @@
       </c>
       <c r="F1375" s="44" t="inlineStr">
         <is>
-          <t>场景1: 批量启用PAT Target — 57%
-场景2: 批量暂停PAT Target — 42%</t>
+          <t>场景1: SP手动广告组新增商品定向PAT(含后置清理,可重复) (PASS)
+场景2: 场景1_批量启用PAT Target — 57% (PASS)
+场景3: 场景2_批量暂停PAT Target — 42% (PASS)
+场景4: 场景1_SD广告组新增ASIN商品定向PAT(含后置清理,可重复) — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -46961,7 +49098,7 @@
       </c>
       <c r="F1378" t="inlineStr">
         <is>
-          <t>按clientId批量重新纳管</t>
+          <t>场景1: 按clientId批量重新纳管</t>
         </is>
       </c>
     </row>
@@ -46989,7 +49126,7 @@
       </c>
       <c r="F1379" t="inlineStr">
         <is>
-          <t>按profileId查已选中账号 — 100.0%</t>
+          <t>场景1: 按profileId查已选中账号 — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47017,7 +49154,7 @@
       </c>
       <c r="F1380" t="inlineStr">
         <is>
-          <t>批量检查profile纳管状态</t>
+          <t>场景1: 批量检查profile纳管状态 (PASS)</t>
         </is>
       </c>
     </row>
@@ -47045,7 +49182,7 @@
       </c>
       <c r="F1381" t="inlineStr">
         <is>
-          <t>查询当前用户是否被纳管 — 100.0%</t>
+          <t>场景1: 查询当前用户是否被纳管 — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47073,7 +49210,8 @@
       </c>
       <c r="F1382" t="inlineStr">
         <is>
-          <t>创建品牌(含后置清理,可重复) — 100.0%</t>
+          <t>场景1: 创建品牌(含后置清理,可重复) — 100.0% (PASS)
+场景2: 更新品牌名(含前置创建/后置清理,可重复) (PASS)</t>
         </is>
       </c>
     </row>
@@ -47099,6 +49237,12 @@
           <t>guguangjie</t>
         </is>
       </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>场景1: 创建品牌(含后置清理,可重复) — 100.0% (PASS)
+场景2: 更新品牌名(含前置创建/后置清理,可重复) (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="1384">
       <c r="A1384" s="41" t="n"/>
@@ -47124,8 +49268,8 @@
       </c>
       <c r="F1384" s="39" t="inlineStr">
         <is>
-          <t>按isManage=1过滤已纳管账号 — 52.8%
-不带过滤条件查询全部账号 — 47.2%</t>
+          <t>场景1: 按isManage=1过滤已纳管账号 — 52.8% (PASS)
+场景2: 不带过滤条件查询全部账号 — 47.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47153,7 +49297,7 @@
       </c>
       <c r="F1385" t="inlineStr">
         <is>
-          <t>查询亚马逊授权列表 — 100.0%</t>
+          <t>场景1: 查询亚马逊授权列表 — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47181,10 +49325,10 @@
       </c>
       <c r="F1386" s="39" t="inlineStr">
         <is>
-          <t>查未纳管账号,不带过滤 — 84.2%
-查已纳管账号,不带过滤 — 4.2%
-已纳管账号按DSP平台类型过滤 — 4.6%
-未纳管账号按profileId搜索 — 4.2%</t>
+          <t>场景1: 查未纳管账号,不带过滤 — 84.2% (PASS)
+场景2: 查已纳管账号,不带过滤 — 4.2% (PASS)
+场景3: 已纳管账号按DSP平台类型过滤 — 4.6% (PASS)
+场景4: 未纳管账号按profileId搜索 — 4.2% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47212,7 +49356,7 @@
       </c>
       <c r="F1387" t="inlineStr">
         <is>
-          <t>分页查询账号列表 — 100.0%</t>
+          <t>场景1: 分页查询账号列表 — 100.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47240,8 +49384,8 @@
       </c>
       <c r="F1388" s="39" t="inlineStr">
         <is>
-          <t>查单个profile的品牌 — 62.6%
-批量查多个profile的品牌 — 37.4%</t>
+          <t>场景1: 查单个profile的品牌 — 62.6% (PASS)
+场景2: 批量查多个profile的品牌 — 37.4% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47269,8 +49413,8 @@
       </c>
       <c r="F1389" s="39" t="inlineStr">
         <is>
-          <t>查单个profile的品牌列表 — 41.0%
-批量查多个profile的品牌列表 — 59.0%</t>
+          <t>场景1: 查单个profile的品牌列表 — 41.0% (PASS)
+场景2: 批量查多个profile的品牌列表 — 59.0% (PASS)</t>
         </is>
       </c>
     </row>
@@ -47298,7 +49442,7 @@
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>按userId查用户详情</t>
+          <t>场景1: 按userId查用户详情 (PASS)</t>
         </is>
       </c>
     </row>
@@ -47326,7 +49470,7 @@
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>设置单个账号纳管状态</t>
+          <t>场景1: 设置单个账号纳管状态</t>
         </is>
       </c>
     </row>
@@ -47354,8 +49498,8 @@
       </c>
       <c r="F1392" s="39" t="inlineStr">
         <is>
-          <t>批量开启纳管 — 37.4%
-批量关闭纳管 — 62.6%</t>
+          <t>场景1: 批量开启纳管 — 37.4%
+场景2: 批量关闭纳管 — 62.6%</t>
         </is>
       </c>
     </row>
@@ -47383,7 +49527,7 @@
       </c>
       <c r="F1393" t="inlineStr">
         <is>
-          <t>移除标签匹配规则(调试接口)</t>
+          <t>场景1: 移除标签匹配规则(调试接口) (PASS)</t>
         </is>
       </c>
     </row>
@@ -47411,7 +49555,7 @@
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>更新品牌名(含前置创建/后置清理,可重复)</t>
+          <t>场景1: 更新品牌名(含前置创建/后置清理,可重复) (PASS)</t>
         </is>
       </c>
     </row>
@@ -47439,7 +49583,7 @@
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>修改用户邮箱</t>
+          <t>场景1: 修改用户邮箱</t>
         </is>
       </c>
     </row>
@@ -47467,7 +49611,7 @@
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>修改用户密码</t>
+          <t>场景1: 修改用户密码</t>
         </is>
       </c>
     </row>

--- a/single-api/mainapi/swagger_modules.xlsx
+++ b/single-api/mainapi/swagger_modules.xlsx
@@ -324,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -465,6 +465,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -831,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:J131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -888,6 +891,11 @@
           <t>接口覆盖率</t>
         </is>
       </c>
+      <c r="J1" s="47" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="43" t="inlineStr">
@@ -929,6 +937,11 @@
       <c r="I2" s="29" t="inlineStr">
         <is>
           <t>100% (3/3)</t>
+        </is>
+      </c>
+      <c r="J2" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\AdGroup</t>
         </is>
       </c>
     </row>
@@ -970,6 +983,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J3" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\AdGroupTag</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="41" t="n"/>
@@ -1009,6 +1027,11 @@
           <t>83% (5/6)</t>
         </is>
       </c>
+      <c r="J4" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\Ads</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="n"/>
@@ -1048,6 +1071,11 @@
           <t>100% (7/7)</t>
         </is>
       </c>
+      <c r="J5" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\AsinTag</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="41" t="n"/>
@@ -1087,6 +1115,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J6" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="41" t="n"/>
@@ -1126,6 +1159,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J7" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\CampaignPlacement</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="41" t="n"/>
@@ -1165,6 +1203,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J8" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\CampaignTag</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="41" t="n"/>
@@ -1204,6 +1247,11 @@
           <t>100% (25/25)</t>
         </is>
       </c>
+      <c r="J9" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="41" t="n"/>
@@ -1243,6 +1291,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="J10" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\EasySqlTest</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="41" t="n"/>
@@ -1282,6 +1335,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J11" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\Health</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="41" t="n"/>
@@ -1321,6 +1379,11 @@
           <t>75% (3/4)</t>
         </is>
       </c>
+      <c r="J12" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\Keyword</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="41" t="n"/>
@@ -1360,6 +1423,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J13" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\KeywordTag</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="41" t="n"/>
@@ -1399,6 +1467,11 @@
           <t>100% (6/6)</t>
         </is>
       </c>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\KeywordTagAi</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="41" t="n"/>
@@ -1438,6 +1511,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J15" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\McpData</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="41" t="n"/>
@@ -1477,6 +1555,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J16" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\NegativeTarget</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="41" t="n"/>
@@ -1516,6 +1599,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J17" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\ProductAd</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="41" t="n"/>
@@ -1555,6 +1643,11 @@
           <t>94% (15/16)</t>
         </is>
       </c>
+      <c r="J18" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\PromptAdExtension</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="41" t="n"/>
@@ -1594,6 +1687,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="J19" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\SearchTerm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="41" t="n"/>
@@ -1633,6 +1731,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J20" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\SupplementData</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="41" t="n"/>
@@ -1672,6 +1775,11 @@
           <t>82% (9/11)</t>
         </is>
       </c>
+      <c r="J21" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\Target</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="41" t="n"/>
@@ -1711,6 +1819,11 @@
           <t>0% (0/6)</t>
         </is>
       </c>
+      <c r="J22" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\Amazon.Advertising.Api\WeatherForecast</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="41" t="n"/>
@@ -1746,6 +1859,11 @@
           <t>0% (0/25)</t>
         </is>
       </c>
+      <c r="J23" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AI</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="41" t="n"/>
@@ -1781,6 +1899,11 @@
           <t>56% (5/9)</t>
         </is>
       </c>
+      <c r="J24" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AIManage</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="41" t="n"/>
@@ -1816,6 +1939,11 @@
           <t>63% (17/27)</t>
         </is>
       </c>
+      <c r="J25" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Account</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="n"/>
@@ -1851,6 +1979,11 @@
           <t>83% (15/18)</t>
         </is>
       </c>
+      <c r="J26" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Ad</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="n"/>
@@ -1886,6 +2019,11 @@
           <t>50% (2/4)</t>
         </is>
       </c>
+      <c r="J27" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AdExtension</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="41" t="n"/>
@@ -1921,6 +2059,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J28" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AdGroupTag</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="n"/>
@@ -1956,6 +2099,11 @@
           <t>17% (1/6)</t>
         </is>
       </c>
+      <c r="J29" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AdGroupUpdate</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="41" t="n"/>
@@ -1991,6 +2139,11 @@
           <t>84% (26/31)</t>
         </is>
       </c>
+      <c r="J30" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Adgroup</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="41" t="n"/>
@@ -2026,6 +2179,11 @@
           <t>100% (12/12)</t>
         </is>
       </c>
+      <c r="J31" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AdvertisingDeal</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="n"/>
@@ -2061,6 +2219,11 @@
           <t>33% (3/9)</t>
         </is>
       </c>
+      <c r="J32" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AmazonAds</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="41" t="n"/>
@@ -2096,6 +2259,11 @@
           <t>100% (6/6)</t>
         </is>
       </c>
+      <c r="J33" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AmazonAiImage</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="41" t="n"/>
@@ -2131,6 +2299,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="J34" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AmazonApi</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="41" t="n"/>
@@ -2166,6 +2339,11 @@
           <t>86% (6/7)</t>
         </is>
       </c>
+      <c r="J35" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AmazonAttribution</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="41" t="n"/>
@@ -2201,6 +2379,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J36" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AmazonAudience</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="41" t="n"/>
@@ -2236,6 +2419,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J37" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AmsAudit</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="41" t="n"/>
@@ -2271,6 +2459,11 @@
           <t>100% (18/18)</t>
         </is>
       </c>
+      <c r="J38" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AnalyticsDashboard</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="41" t="n"/>
@@ -2306,6 +2499,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="J39" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AnlayticShare</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="41" t="n"/>
@@ -2341,6 +2539,11 @@
           <t>94% (17/18)</t>
         </is>
       </c>
+      <c r="J40" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Asin</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="41" t="n"/>
@@ -2376,6 +2579,11 @@
           <t>100% (6/6)</t>
         </is>
       </c>
+      <c r="J41" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\AsinTag</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="41" t="n"/>
@@ -2411,6 +2619,11 @@
           <t>100% (16/16)</t>
         </is>
       </c>
+      <c r="J42" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Benchmark</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="41" t="n"/>
@@ -2446,6 +2659,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="J43" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Brand</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="41" t="n"/>
@@ -2481,6 +2699,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J44" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\BrandAudit</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="41" t="n"/>
@@ -2516,6 +2739,11 @@
           <t>96% (95/99)</t>
         </is>
       </c>
+      <c r="J45" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Budget</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="41" t="n"/>
@@ -2551,6 +2779,11 @@
           <t>97% (37/38)</t>
         </is>
       </c>
+      <c r="J46" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\BulkCampaign</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="41" t="n"/>
@@ -2586,6 +2819,11 @@
           <t>74% (67/90)</t>
         </is>
       </c>
+      <c r="J47" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\BulkOperate</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="41" t="n"/>
@@ -2621,6 +2859,11 @@
           <t>100% (106/106)</t>
         </is>
       </c>
+      <c r="J48" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Campaign</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="41" t="n"/>
@@ -2656,6 +2899,11 @@
           <t>100% (28/28)</t>
         </is>
       </c>
+      <c r="J49" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignCreate</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="41" t="n"/>
@@ -2691,6 +2939,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="J50" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignExplorer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="41" t="n"/>
@@ -2726,6 +2979,11 @@
           <t>100% (9/9)</t>
         </is>
       </c>
+      <c r="J51" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignMapping</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="41" t="n"/>
@@ -2761,6 +3019,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J52" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignMaterials</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="41" t="n"/>
@@ -2796,6 +3059,11 @@
           <t>62% (47/76)</t>
         </is>
       </c>
+      <c r="J53" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignPartial</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="41" t="n"/>
@@ -2831,6 +3099,11 @@
           <t>82% (23/28)</t>
         </is>
       </c>
+      <c r="J54" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignSponsoredBrandCreate</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="41" t="n"/>
@@ -2866,6 +3139,11 @@
           <t>100% (9/9)</t>
         </is>
       </c>
+      <c r="J55" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignTag</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="41" t="n"/>
@@ -2901,6 +3179,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J56" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CampaignUpdate</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="41" t="n"/>
@@ -2936,6 +3219,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J57" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Copilot</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="41" t="n"/>
@@ -2971,6 +3259,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J58" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CreativeHub</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="41" t="n"/>
@@ -3006,6 +3299,11 @@
           <t>75% (6/8)</t>
         </is>
       </c>
+      <c r="J59" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\CustomizationFuction</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="41" t="n"/>
@@ -3041,6 +3339,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J60" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="41" t="n"/>
@@ -3076,6 +3379,11 @@
           <t>100% (66/66)</t>
         </is>
       </c>
+      <c r="J61" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\DefaultReport</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="41" t="n"/>
@@ -3111,6 +3419,11 @@
           <t>50% (3/6)</t>
         </is>
       </c>
+      <c r="J62" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\DownloadCenter</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="41" t="n"/>
@@ -3146,6 +3459,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J63" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ExchangeRate</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="41" t="n"/>
@@ -3181,6 +3499,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J64" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Explorer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="41" t="n"/>
@@ -3216,6 +3539,11 @@
           <t>40% (10/25)</t>
         </is>
       </c>
+      <c r="J65" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Fead</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="41" t="n"/>
@@ -3251,6 +3579,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J66" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\File</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="41" t="n"/>
@@ -3286,6 +3619,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J67" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\H10</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="41" t="n"/>
@@ -3321,6 +3659,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J68" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Health</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="41" t="n"/>
@@ -3356,6 +3699,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J69" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Histroy</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="41" t="n"/>
@@ -3391,6 +3739,11 @@
           <t>100% (6/6)</t>
         </is>
       </c>
+      <c r="J70" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\HolidayKeyword</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="41" t="n"/>
@@ -3426,6 +3779,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J71" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\HolidayManager</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="41" t="n"/>
@@ -3461,6 +3819,11 @@
           <t>100% (18/18)</t>
         </is>
       </c>
+      <c r="J72" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\HourlyExplorer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="41" t="n"/>
@@ -3496,6 +3859,11 @@
           <t>100% (18/18)</t>
         </is>
       </c>
+      <c r="J73" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Incrementality</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="41" t="n"/>
@@ -3531,6 +3899,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J74" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ItsumoKeyword</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="41" t="n"/>
@@ -3566,6 +3939,11 @@
           <t>100% (63/63)</t>
         </is>
       </c>
+      <c r="J75" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Keyword</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="41" t="n"/>
@@ -3601,6 +3979,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="J76" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\KeywordTag</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="41" t="n"/>
@@ -3636,6 +4019,11 @@
           <t>57% (4/7)</t>
         </is>
       </c>
+      <c r="J77" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\LoginOauth</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="41" t="n"/>
@@ -3671,6 +4059,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J78" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Marketplace</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="41" t="n"/>
@@ -3706,6 +4099,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="J79" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\MarketplaceDashboard</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="41" t="n"/>
@@ -3741,6 +4139,11 @@
           <t>100% (23/23)</t>
         </is>
       </c>
+      <c r="J80" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\MedianPlan</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="41" t="n"/>
@@ -3776,6 +4179,11 @@
           <t>100% (26/26)</t>
         </is>
       </c>
+      <c r="J81" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\NegativeKeywordList</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="41" t="n"/>
@@ -3811,6 +4219,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J82" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\NegativePATList</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="41" t="n"/>
@@ -3846,6 +4259,11 @@
           <t>100% (7/7)</t>
         </is>
       </c>
+      <c r="J83" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\NegativeTargeting</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="41" t="n"/>
@@ -3881,6 +4299,11 @@
           <t>100% (20/20)</t>
         </is>
       </c>
+      <c r="J84" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Notification</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="41" t="n"/>
@@ -3916,6 +4339,11 @@
           <t>100% (7/7)</t>
         </is>
       </c>
+      <c r="J85" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Oauth2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="41" t="n"/>
@@ -3951,6 +4379,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J86" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\OperateLog</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="41" t="n"/>
@@ -3986,6 +4419,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J87" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\OptimizationRule</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="41" t="n"/>
@@ -4021,6 +4459,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J88" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Portfolio</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="41" t="n"/>
@@ -4056,6 +4499,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J89" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\PortfolioFromAmz</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="41" t="n"/>
@@ -4091,6 +4539,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J90" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ProductAd</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="41" t="n"/>
@@ -4126,6 +4579,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J91" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ProductAdPartial</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="41" t="n"/>
@@ -4161,6 +4619,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J92" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ProductCenter</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="41" t="n"/>
@@ -4196,6 +4659,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J93" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ProductEligibility</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="41" t="n"/>
@@ -4231,6 +4699,11 @@
           <t>100% (6/6)</t>
         </is>
       </c>
+      <c r="J94" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ProductTracking</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="41" t="n"/>
@@ -4266,6 +4739,11 @@
           <t>91% (10/11)</t>
         </is>
       </c>
+      <c r="J95" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Profile</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="41" t="n"/>
@@ -4301,6 +4779,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J96" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\PromptInsight</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="41" t="n"/>
@@ -4336,6 +4819,11 @@
           <t>100% (18/18)</t>
         </is>
       </c>
+      <c r="J97" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Research</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="41" t="n"/>
@@ -4371,6 +4859,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J98" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SCPAnalysis</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="41" t="n"/>
@@ -4406,6 +4899,11 @@
           <t>100% (13/13)</t>
         </is>
       </c>
+      <c r="J99" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SQPAnalysis</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="41" t="n"/>
@@ -4441,6 +4939,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J100" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SSOLogin</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="41" t="n"/>
@@ -4476,6 +4979,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J101" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SaveToReport</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="41" t="n"/>
@@ -4511,6 +5019,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J102" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SearchTerm</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="41" t="n"/>
@@ -4546,6 +5059,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="J103" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Setting</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="41" t="n"/>
@@ -4581,6 +5099,11 @@
           <t>15% (2/13)</t>
         </is>
       </c>
+      <c r="J104" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Share</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="41" t="n"/>
@@ -4616,6 +5139,11 @@
           <t>100% (2/2)</t>
         </is>
       </c>
+      <c r="J105" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Sov</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="41" t="n"/>
@@ -4651,6 +5179,11 @@
           <t>100% (8/8)</t>
         </is>
       </c>
+      <c r="J106" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredBrand</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="41" t="n"/>
@@ -4686,6 +5219,11 @@
           <t>100% (4/4)</t>
         </is>
       </c>
+      <c r="J107" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredBrandMaterial</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="41" t="n"/>
@@ -4721,6 +5259,11 @@
           <t>100% (11/11)</t>
         </is>
       </c>
+      <c r="J108" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredBrandMigrate</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="41" t="n"/>
@@ -4756,6 +5299,11 @@
           <t>100% (14/14)</t>
         </is>
       </c>
+      <c r="J109" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredDisplay</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="41" t="n"/>
@@ -4791,6 +5339,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J110" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredDisplayMaterial</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="41" t="n"/>
@@ -4826,6 +5379,11 @@
           <t>100% (7/7)</t>
         </is>
       </c>
+      <c r="J111" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredProducts</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="41" t="n"/>
@@ -4861,6 +5419,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J112" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredTelevise</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="41" t="n"/>
@@ -4896,6 +5459,11 @@
           <t>100% (3/3)</t>
         </is>
       </c>
+      <c r="J113" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SponsoredTeleviseMaterial</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="41" t="n"/>
@@ -4931,6 +5499,11 @@
           <t>100% (10/10)</t>
         </is>
       </c>
+      <c r="J114" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\SyncData</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="41" t="n"/>
@@ -4966,6 +5539,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J115" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Tag</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="41" t="n"/>
@@ -5001,6 +5579,11 @@
           <t>84% (49/58)</t>
         </is>
       </c>
+      <c r="J116" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Tagging</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="41" t="n"/>
@@ -5036,6 +5619,11 @@
           <t>41% (9/22)</t>
         </is>
       </c>
+      <c r="J117" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Targeting</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="41" t="n"/>
@@ -5071,6 +5659,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J118" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\Test</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="41" t="n"/>
@@ -5106,6 +5699,11 @@
           <t>100% (1/1)</t>
         </is>
       </c>
+      <c r="J119" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\ThreadsCount</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="41" t="n"/>
@@ -5141,6 +5739,11 @@
           <t>100% (19/19)</t>
         </is>
       </c>
+      <c r="J120" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\User</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="41" t="n"/>
@@ -5176,6 +5779,11 @@
           <t>100% (5/5)</t>
         </is>
       </c>
+      <c r="J121" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\UserGroup</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="41" t="n"/>
@@ -5211,6 +5819,11 @@
           <t>70% (21/30)</t>
         </is>
       </c>
+      <c r="J122" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\WarRoom</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="41" t="n"/>
@@ -5244,6 +5857,11 @@
       <c r="I123" t="inlineStr">
         <is>
           <t>100% (15/15)</t>
+        </is>
+      </c>
+      <c r="J123" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\PacvueMainApi\WeatherForecast</t>
         </is>
       </c>
     </row>
@@ -5315,6 +5933,11 @@
           <t>接口数</t>
         </is>
       </c>
+      <c r="J128" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\负责人\模块数</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="41" t="n"/>
@@ -5330,6 +5953,11 @@
       <c r="E129" s="15" t="n">
         <v>528</v>
       </c>
+      <c r="J129" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\zhanghaobo\41</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="41" t="n"/>
@@ -5345,6 +5973,11 @@
       <c r="E130" s="17" t="n">
         <v>649</v>
       </c>
+      <c r="J130" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\guguangjie\41</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="42" t="n"/>
@@ -5359,6 +5992,11 @@
       </c>
       <c r="E131" s="19" t="n">
         <v>403</v>
+      </c>
+      <c r="J131" s="51" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\mainapi\us\limin\40</t>
+        </is>
       </c>
     </row>
   </sheetData>
